--- a/three_way_finance_model.xlsx
+++ b/three_way_finance_model.xlsx
@@ -18,12 +18,14 @@
     <sheet name="REFM" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Frontier" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="RAB" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="PTRM" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Initiatives" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Income Statement" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Balance Sheet" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Cash Flow" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Checks" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="RAB Roll-Forward" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="PTRM" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Dep Tracking" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Initiatives" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Income Statement" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Balance Sheet" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Cash Flow" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Checks" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -151,7 +153,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -245,7 +247,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="004B0082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="000070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -263,11 +275,6 @@
         <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -281,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -440,15 +447,21 @@
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="18" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="18" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="18" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3144,6 +3157,2535 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004B0082"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>RAB ROLL-FORWARD MODEL — Detailed by Asset Class (AER Standard Lives)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>$AUD Millions</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>FY2019A</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>FY2020A</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>FY2021A</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>FY2022A</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>FY2023A</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>FY2024E</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>FY2025E</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="M2" s="14" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="O2" s="14" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="P2" s="14" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>TRANSMISSION LINES  |  AER Standard Life: 60 years</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="n"/>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="16" t="n"/>
+      <c r="K4" s="16" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="16" t="n"/>
+      <c r="O4" s="16" t="n"/>
+      <c r="P4" s="16" t="n"/>
+      <c r="Q4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Opening RAB ($M)</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C5" s="26" t="n">
+        <v>2536</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>2689.3</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>2857.9</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>3073.5</v>
+      </c>
+      <c r="G5" s="39">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="H5" s="39">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="I5" s="39">
+        <f>H9</f>
+        <v/>
+      </c>
+      <c r="J5" s="39">
+        <f>I9</f>
+        <v/>
+      </c>
+      <c r="K5" s="39">
+        <f>J9</f>
+        <v/>
+      </c>
+      <c r="L5" s="39">
+        <f>K9</f>
+        <v/>
+      </c>
+      <c r="M5" s="39">
+        <f>L9</f>
+        <v/>
+      </c>
+      <c r="N5" s="39">
+        <f>M9</f>
+        <v/>
+      </c>
+      <c r="O5" s="39">
+        <f>N9</f>
+        <v/>
+      </c>
+      <c r="P5" s="39">
+        <f>O9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + CPI Indexation</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="G6" s="39">
+        <f>G5*Assumptions!G15</f>
+        <v/>
+      </c>
+      <c r="H6" s="39">
+        <f>H5*Assumptions!H15</f>
+        <v/>
+      </c>
+      <c r="I6" s="39">
+        <f>I5*Assumptions!I15</f>
+        <v/>
+      </c>
+      <c r="J6" s="39">
+        <f>J5*Assumptions!J15</f>
+        <v/>
+      </c>
+      <c r="K6" s="39">
+        <f>K5*Assumptions!K15</f>
+        <v/>
+      </c>
+      <c r="L6" s="39">
+        <f>L5*Assumptions!L15</f>
+        <v/>
+      </c>
+      <c r="M6" s="39">
+        <f>M5*Assumptions!M15</f>
+        <v/>
+      </c>
+      <c r="N6" s="39">
+        <f>N5*Assumptions!N15</f>
+        <v/>
+      </c>
+      <c r="O6" s="39">
+        <f>O5*Assumptions!O15</f>
+        <v/>
+      </c>
+      <c r="P6" s="39">
+        <f>P5*Assumptions!P15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + Capex Additions (×50% allocation)</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>140</v>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>165</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>190</v>
+      </c>
+      <c r="G7" s="39">
+        <f>'Fixed Assets'!G7</f>
+        <v/>
+      </c>
+      <c r="H7" s="39">
+        <f>'Fixed Assets'!H7</f>
+        <v/>
+      </c>
+      <c r="I7" s="39">
+        <f>'Fixed Assets'!I7</f>
+        <v/>
+      </c>
+      <c r="J7" s="39">
+        <f>'Fixed Assets'!J7</f>
+        <v/>
+      </c>
+      <c r="K7" s="39">
+        <f>'Fixed Assets'!K7</f>
+        <v/>
+      </c>
+      <c r="L7" s="39">
+        <f>'Fixed Assets'!L7</f>
+        <v/>
+      </c>
+      <c r="M7" s="39">
+        <f>'Fixed Assets'!M7</f>
+        <v/>
+      </c>
+      <c r="N7" s="39">
+        <f>'Fixed Assets'!N7</f>
+        <v/>
+      </c>
+      <c r="O7" s="39">
+        <f>'Fixed Assets'!O7</f>
+        <v/>
+      </c>
+      <c r="P7" s="39">
+        <f>'Fixed Assets'!P7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    − Regulatory Depreciation  (÷ 60 yr AER life)</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="G8" s="39">
+        <f>G5/60</f>
+        <v/>
+      </c>
+      <c r="H8" s="39">
+        <f>H5/60</f>
+        <v/>
+      </c>
+      <c r="I8" s="39">
+        <f>I5/60</f>
+        <v/>
+      </c>
+      <c r="J8" s="39">
+        <f>J5/60</f>
+        <v/>
+      </c>
+      <c r="K8" s="39">
+        <f>K5/60</f>
+        <v/>
+      </c>
+      <c r="L8" s="39">
+        <f>L5/60</f>
+        <v/>
+      </c>
+      <c r="M8" s="39">
+        <f>M5/60</f>
+        <v/>
+      </c>
+      <c r="N8" s="39">
+        <f>N5/60</f>
+        <v/>
+      </c>
+      <c r="O8" s="39">
+        <f>O5/60</f>
+        <v/>
+      </c>
+      <c r="P8" s="39">
+        <f>P5/60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    = Closing RAB</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n">
+        <v>2536</v>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>2689.3</v>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>2857.9</v>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>3073.5</v>
+      </c>
+      <c r="F9" s="43" t="n">
+        <v>3396.7</v>
+      </c>
+      <c r="G9" s="44">
+        <f>G5+G6+G7-G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="44">
+        <f>H5+H6+H7-H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="44">
+        <f>I5+I6+I7-I8</f>
+        <v/>
+      </c>
+      <c r="J9" s="44">
+        <f>J5+J6+J7-J8</f>
+        <v/>
+      </c>
+      <c r="K9" s="44">
+        <f>K5+K6+K7-K8</f>
+        <v/>
+      </c>
+      <c r="L9" s="44">
+        <f>L5+L6+L7-L8</f>
+        <v/>
+      </c>
+      <c r="M9" s="44">
+        <f>M5+M6+M7-M8</f>
+        <v/>
+      </c>
+      <c r="N9" s="44">
+        <f>N5+N6+N7-N8</f>
+        <v/>
+      </c>
+      <c r="O9" s="44">
+        <f>O5+O6+O7-O8</f>
+        <v/>
+      </c>
+      <c r="P9" s="44">
+        <f>P5+P6+P7-P8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>SUBSTATIONS  |  AER Standard Life: 55 years</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="16" t="n"/>
+      <c r="Q11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Opening RAB ($M)</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>1440</v>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>1519.4</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>1609.1</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>1707.8</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>1834.4</v>
+      </c>
+      <c r="G12" s="39">
+        <f>F16</f>
+        <v/>
+      </c>
+      <c r="H12" s="39">
+        <f>G16</f>
+        <v/>
+      </c>
+      <c r="I12" s="39">
+        <f>H16</f>
+        <v/>
+      </c>
+      <c r="J12" s="39">
+        <f>I16</f>
+        <v/>
+      </c>
+      <c r="K12" s="39">
+        <f>J16</f>
+        <v/>
+      </c>
+      <c r="L12" s="39">
+        <f>K16</f>
+        <v/>
+      </c>
+      <c r="M12" s="39">
+        <f>L16</f>
+        <v/>
+      </c>
+      <c r="N12" s="39">
+        <f>M16</f>
+        <v/>
+      </c>
+      <c r="O12" s="39">
+        <f>N16</f>
+        <v/>
+      </c>
+      <c r="P12" s="39">
+        <f>O16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + CPI Indexation</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="G13" s="39">
+        <f>G12*Assumptions!G15</f>
+        <v/>
+      </c>
+      <c r="H13" s="39">
+        <f>H12*Assumptions!H15</f>
+        <v/>
+      </c>
+      <c r="I13" s="39">
+        <f>I12*Assumptions!I15</f>
+        <v/>
+      </c>
+      <c r="J13" s="39">
+        <f>J12*Assumptions!J15</f>
+        <v/>
+      </c>
+      <c r="K13" s="39">
+        <f>K12*Assumptions!K15</f>
+        <v/>
+      </c>
+      <c r="L13" s="39">
+        <f>L12*Assumptions!L15</f>
+        <v/>
+      </c>
+      <c r="M13" s="39">
+        <f>M12*Assumptions!M15</f>
+        <v/>
+      </c>
+      <c r="N13" s="39">
+        <f>N12*Assumptions!N15</f>
+        <v/>
+      </c>
+      <c r="O13" s="39">
+        <f>O12*Assumptions!O15</f>
+        <v/>
+      </c>
+      <c r="P13" s="39">
+        <f>P12*Assumptions!P15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + Capex Additions (×30% allocation)</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>114</v>
+      </c>
+      <c r="G14" s="39">
+        <f>'Fixed Assets'!G15</f>
+        <v/>
+      </c>
+      <c r="H14" s="39">
+        <f>'Fixed Assets'!H15</f>
+        <v/>
+      </c>
+      <c r="I14" s="39">
+        <f>'Fixed Assets'!I15</f>
+        <v/>
+      </c>
+      <c r="J14" s="39">
+        <f>'Fixed Assets'!J15</f>
+        <v/>
+      </c>
+      <c r="K14" s="39">
+        <f>'Fixed Assets'!K15</f>
+        <v/>
+      </c>
+      <c r="L14" s="39">
+        <f>'Fixed Assets'!L15</f>
+        <v/>
+      </c>
+      <c r="M14" s="39">
+        <f>'Fixed Assets'!M15</f>
+        <v/>
+      </c>
+      <c r="N14" s="39">
+        <f>'Fixed Assets'!N15</f>
+        <v/>
+      </c>
+      <c r="O14" s="39">
+        <f>'Fixed Assets'!O15</f>
+        <v/>
+      </c>
+      <c r="P14" s="39">
+        <f>'Fixed Assets'!P15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    − Regulatory Depreciation  (÷ 55 yr AER life)</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G15" s="39">
+        <f>G12/55</f>
+        <v/>
+      </c>
+      <c r="H15" s="39">
+        <f>H12/55</f>
+        <v/>
+      </c>
+      <c r="I15" s="39">
+        <f>I12/55</f>
+        <v/>
+      </c>
+      <c r="J15" s="39">
+        <f>J12/55</f>
+        <v/>
+      </c>
+      <c r="K15" s="39">
+        <f>K12/55</f>
+        <v/>
+      </c>
+      <c r="L15" s="39">
+        <f>L12/55</f>
+        <v/>
+      </c>
+      <c r="M15" s="39">
+        <f>M12/55</f>
+        <v/>
+      </c>
+      <c r="N15" s="39">
+        <f>N12/55</f>
+        <v/>
+      </c>
+      <c r="O15" s="39">
+        <f>O12/55</f>
+        <v/>
+      </c>
+      <c r="P15" s="39">
+        <f>P12/55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    = Closing RAB</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="n">
+        <v>1519.4</v>
+      </c>
+      <c r="C16" s="43" t="n">
+        <v>1609.1</v>
+      </c>
+      <c r="D16" s="43" t="n">
+        <v>1707.8</v>
+      </c>
+      <c r="E16" s="43" t="n">
+        <v>1834.4</v>
+      </c>
+      <c r="F16" s="43" t="n">
+        <v>2025.1</v>
+      </c>
+      <c r="G16" s="44">
+        <f>G12+G13+G14-G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="44">
+        <f>H12+H13+H14-H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="44">
+        <f>I12+I13+I14-I15</f>
+        <v/>
+      </c>
+      <c r="J16" s="44">
+        <f>J12+J13+J14-J15</f>
+        <v/>
+      </c>
+      <c r="K16" s="44">
+        <f>K12+K13+K14-K15</f>
+        <v/>
+      </c>
+      <c r="L16" s="44">
+        <f>L12+L13+L14-L15</f>
+        <v/>
+      </c>
+      <c r="M16" s="44">
+        <f>M12+M13+M14-M15</f>
+        <v/>
+      </c>
+      <c r="N16" s="44">
+        <f>N12+N13+N14-N15</f>
+        <v/>
+      </c>
+      <c r="O16" s="44">
+        <f>O12+O13+O14-O15</f>
+        <v/>
+      </c>
+      <c r="P16" s="44">
+        <f>P12+P13+P14-P15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>TRANSFORMERS  |  AER Standard Life: 45 years</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="n"/>
+      <c r="K18" s="16" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Opening RAB ($M)</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n">
+        <v>480</v>
+      </c>
+      <c r="C19" s="26" t="n">
+        <v>504.5</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>532.4</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>563.2</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>603.1</v>
+      </c>
+      <c r="G19" s="39">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="H19" s="39">
+        <f>G23</f>
+        <v/>
+      </c>
+      <c r="I19" s="39">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="J19" s="39">
+        <f>I23</f>
+        <v/>
+      </c>
+      <c r="K19" s="39">
+        <f>J23</f>
+        <v/>
+      </c>
+      <c r="L19" s="39">
+        <f>K23</f>
+        <v/>
+      </c>
+      <c r="M19" s="39">
+        <f>L23</f>
+        <v/>
+      </c>
+      <c r="N19" s="39">
+        <f>M23</f>
+        <v/>
+      </c>
+      <c r="O19" s="39">
+        <f>N23</f>
+        <v/>
+      </c>
+      <c r="P19" s="39">
+        <f>O23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + CPI Indexation</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C20" s="26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="G20" s="39">
+        <f>G19*Assumptions!G15</f>
+        <v/>
+      </c>
+      <c r="H20" s="39">
+        <f>H19*Assumptions!H15</f>
+        <v/>
+      </c>
+      <c r="I20" s="39">
+        <f>I19*Assumptions!I15</f>
+        <v/>
+      </c>
+      <c r="J20" s="39">
+        <f>J19*Assumptions!J15</f>
+        <v/>
+      </c>
+      <c r="K20" s="39">
+        <f>K19*Assumptions!K15</f>
+        <v/>
+      </c>
+      <c r="L20" s="39">
+        <f>L19*Assumptions!L15</f>
+        <v/>
+      </c>
+      <c r="M20" s="39">
+        <f>M19*Assumptions!M15</f>
+        <v/>
+      </c>
+      <c r="N20" s="39">
+        <f>N19*Assumptions!N15</f>
+        <v/>
+      </c>
+      <c r="O20" s="39">
+        <f>O19*Assumptions!O15</f>
+        <v/>
+      </c>
+      <c r="P20" s="39">
+        <f>P19*Assumptions!P15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + Capex Additions (×10% allocation)</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="C21" s="26" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F21" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="G21" s="39">
+        <f>'Fixed Assets'!G23</f>
+        <v/>
+      </c>
+      <c r="H21" s="39">
+        <f>'Fixed Assets'!H23</f>
+        <v/>
+      </c>
+      <c r="I21" s="39">
+        <f>'Fixed Assets'!I23</f>
+        <v/>
+      </c>
+      <c r="J21" s="39">
+        <f>'Fixed Assets'!J23</f>
+        <v/>
+      </c>
+      <c r="K21" s="39">
+        <f>'Fixed Assets'!K23</f>
+        <v/>
+      </c>
+      <c r="L21" s="39">
+        <f>'Fixed Assets'!L23</f>
+        <v/>
+      </c>
+      <c r="M21" s="39">
+        <f>'Fixed Assets'!M23</f>
+        <v/>
+      </c>
+      <c r="N21" s="39">
+        <f>'Fixed Assets'!N23</f>
+        <v/>
+      </c>
+      <c r="O21" s="39">
+        <f>'Fixed Assets'!O23</f>
+        <v/>
+      </c>
+      <c r="P21" s="39">
+        <f>'Fixed Assets'!P23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    − Regulatory Depreciation  (÷ 45 yr AER life)</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F22" s="26" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G22" s="39">
+        <f>G19/45</f>
+        <v/>
+      </c>
+      <c r="H22" s="39">
+        <f>H19/45</f>
+        <v/>
+      </c>
+      <c r="I22" s="39">
+        <f>I19/45</f>
+        <v/>
+      </c>
+      <c r="J22" s="39">
+        <f>J19/45</f>
+        <v/>
+      </c>
+      <c r="K22" s="39">
+        <f>K19/45</f>
+        <v/>
+      </c>
+      <c r="L22" s="39">
+        <f>L19/45</f>
+        <v/>
+      </c>
+      <c r="M22" s="39">
+        <f>M19/45</f>
+        <v/>
+      </c>
+      <c r="N22" s="39">
+        <f>N19/45</f>
+        <v/>
+      </c>
+      <c r="O22" s="39">
+        <f>O19/45</f>
+        <v/>
+      </c>
+      <c r="P22" s="39">
+        <f>P19/45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    = Closing RAB</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="n">
+        <v>504.5</v>
+      </c>
+      <c r="C23" s="43" t="n">
+        <v>532.4</v>
+      </c>
+      <c r="D23" s="43" t="n">
+        <v>563.2</v>
+      </c>
+      <c r="E23" s="43" t="n">
+        <v>603.1</v>
+      </c>
+      <c r="F23" s="43" t="n">
+        <v>663.9</v>
+      </c>
+      <c r="G23" s="44">
+        <f>G19+G20+G21-G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="44">
+        <f>H19+H20+H21-H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="44">
+        <f>I19+I20+I21-I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="44">
+        <f>J19+J20+J21-J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="44">
+        <f>K19+K20+K21-K22</f>
+        <v/>
+      </c>
+      <c r="L23" s="44">
+        <f>L19+L20+L21-L22</f>
+        <v/>
+      </c>
+      <c r="M23" s="44">
+        <f>M19+M20+M21-M22</f>
+        <v/>
+      </c>
+      <c r="N23" s="44">
+        <f>N19+N20+N21-N22</f>
+        <v/>
+      </c>
+      <c r="O23" s="44">
+        <f>O19+O20+O21-O22</f>
+        <v/>
+      </c>
+      <c r="P23" s="44">
+        <f>P19+P20+P21-P22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>SCADA &amp; CONTROL  |  AER Standard Life: 25 years</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="n"/>
+      <c r="K25" s="16" t="n"/>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="16" t="n"/>
+      <c r="N25" s="16" t="n"/>
+      <c r="O25" s="16" t="n"/>
+      <c r="P25" s="16" t="n"/>
+      <c r="Q25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Opening RAB ($M)</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>336</v>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>347.2</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <v>397</v>
+      </c>
+      <c r="G26" s="39">
+        <f>F30</f>
+        <v/>
+      </c>
+      <c r="H26" s="39">
+        <f>G30</f>
+        <v/>
+      </c>
+      <c r="I26" s="39">
+        <f>H30</f>
+        <v/>
+      </c>
+      <c r="J26" s="39">
+        <f>I30</f>
+        <v/>
+      </c>
+      <c r="K26" s="39">
+        <f>J30</f>
+        <v/>
+      </c>
+      <c r="L26" s="39">
+        <f>K30</f>
+        <v/>
+      </c>
+      <c r="M26" s="39">
+        <f>L30</f>
+        <v/>
+      </c>
+      <c r="N26" s="39">
+        <f>M30</f>
+        <v/>
+      </c>
+      <c r="O26" s="39">
+        <f>N30</f>
+        <v/>
+      </c>
+      <c r="P26" s="39">
+        <f>O30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + CPI Indexation</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G27" s="39">
+        <f>G26*Assumptions!G15</f>
+        <v/>
+      </c>
+      <c r="H27" s="39">
+        <f>H26*Assumptions!H15</f>
+        <v/>
+      </c>
+      <c r="I27" s="39">
+        <f>I26*Assumptions!I15</f>
+        <v/>
+      </c>
+      <c r="J27" s="39">
+        <f>J26*Assumptions!J15</f>
+        <v/>
+      </c>
+      <c r="K27" s="39">
+        <f>K26*Assumptions!K15</f>
+        <v/>
+      </c>
+      <c r="L27" s="39">
+        <f>L26*Assumptions!L15</f>
+        <v/>
+      </c>
+      <c r="M27" s="39">
+        <f>M26*Assumptions!M15</f>
+        <v/>
+      </c>
+      <c r="N27" s="39">
+        <f>N26*Assumptions!N15</f>
+        <v/>
+      </c>
+      <c r="O27" s="39">
+        <f>O26*Assumptions!O15</f>
+        <v/>
+      </c>
+      <c r="P27" s="39">
+        <f>P26*Assumptions!P15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + Capex Additions (×7% allocation)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G28" s="39">
+        <f>'Fixed Assets'!G31</f>
+        <v/>
+      </c>
+      <c r="H28" s="39">
+        <f>'Fixed Assets'!H31</f>
+        <v/>
+      </c>
+      <c r="I28" s="39">
+        <f>'Fixed Assets'!I31</f>
+        <v/>
+      </c>
+      <c r="J28" s="39">
+        <f>'Fixed Assets'!J31</f>
+        <v/>
+      </c>
+      <c r="K28" s="39">
+        <f>'Fixed Assets'!K31</f>
+        <v/>
+      </c>
+      <c r="L28" s="39">
+        <f>'Fixed Assets'!L31</f>
+        <v/>
+      </c>
+      <c r="M28" s="39">
+        <f>'Fixed Assets'!M31</f>
+        <v/>
+      </c>
+      <c r="N28" s="39">
+        <f>'Fixed Assets'!N31</f>
+        <v/>
+      </c>
+      <c r="O28" s="39">
+        <f>'Fixed Assets'!O31</f>
+        <v/>
+      </c>
+      <c r="P28" s="39">
+        <f>'Fixed Assets'!P31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    − Regulatory Depreciation  (÷ 25 yr AER life)</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C29" s="26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" s="26" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="G29" s="39">
+        <f>G26/25</f>
+        <v/>
+      </c>
+      <c r="H29" s="39">
+        <f>H26/25</f>
+        <v/>
+      </c>
+      <c r="I29" s="39">
+        <f>I26/25</f>
+        <v/>
+      </c>
+      <c r="J29" s="39">
+        <f>J26/25</f>
+        <v/>
+      </c>
+      <c r="K29" s="39">
+        <f>K26/25</f>
+        <v/>
+      </c>
+      <c r="L29" s="39">
+        <f>L26/25</f>
+        <v/>
+      </c>
+      <c r="M29" s="39">
+        <f>M26/25</f>
+        <v/>
+      </c>
+      <c r="N29" s="39">
+        <f>N26/25</f>
+        <v/>
+      </c>
+      <c r="O29" s="39">
+        <f>O26/25</f>
+        <v/>
+      </c>
+      <c r="P29" s="39">
+        <f>P26/25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    = Closing RAB</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="n">
+        <v>347.2</v>
+      </c>
+      <c r="C30" s="43" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="D30" s="43" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="E30" s="43" t="n">
+        <v>397</v>
+      </c>
+      <c r="F30" s="43" t="n">
+        <v>431.5</v>
+      </c>
+      <c r="G30" s="44">
+        <f>G26+G27+G28-G29</f>
+        <v/>
+      </c>
+      <c r="H30" s="44">
+        <f>H26+H27+H28-H29</f>
+        <v/>
+      </c>
+      <c r="I30" s="44">
+        <f>I26+I27+I28-I29</f>
+        <v/>
+      </c>
+      <c r="J30" s="44">
+        <f>J26+J27+J28-J29</f>
+        <v/>
+      </c>
+      <c r="K30" s="44">
+        <f>K26+K27+K28-K29</f>
+        <v/>
+      </c>
+      <c r="L30" s="44">
+        <f>L26+L27+L28-L29</f>
+        <v/>
+      </c>
+      <c r="M30" s="44">
+        <f>M26+M27+M28-M29</f>
+        <v/>
+      </c>
+      <c r="N30" s="44">
+        <f>N26+N27+N28-N29</f>
+        <v/>
+      </c>
+      <c r="O30" s="44">
+        <f>O26+O27+O28-O29</f>
+        <v/>
+      </c>
+      <c r="P30" s="44">
+        <f>P26+P27+P28-P29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>OTHER EQUIPMENT  |  AER Standard Life: 30 years</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="16" t="n"/>
+      <c r="J32" s="16" t="n"/>
+      <c r="K32" s="16" t="n"/>
+      <c r="L32" s="16" t="n"/>
+      <c r="M32" s="16" t="n"/>
+      <c r="N32" s="16" t="n"/>
+      <c r="O32" s="16" t="n"/>
+      <c r="P32" s="16" t="n"/>
+      <c r="Q32" s="16" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Opening RAB ($M)</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="E33" s="26" t="n">
+        <v>164</v>
+      </c>
+      <c r="F33" s="26" t="n">
+        <v>174.1</v>
+      </c>
+      <c r="G33" s="39">
+        <f>F37</f>
+        <v/>
+      </c>
+      <c r="H33" s="39">
+        <f>G37</f>
+        <v/>
+      </c>
+      <c r="I33" s="39">
+        <f>H37</f>
+        <v/>
+      </c>
+      <c r="J33" s="39">
+        <f>I37</f>
+        <v/>
+      </c>
+      <c r="K33" s="39">
+        <f>J37</f>
+        <v/>
+      </c>
+      <c r="L33" s="39">
+        <f>K37</f>
+        <v/>
+      </c>
+      <c r="M33" s="39">
+        <f>L37</f>
+        <v/>
+      </c>
+      <c r="N33" s="39">
+        <f>M37</f>
+        <v/>
+      </c>
+      <c r="O33" s="39">
+        <f>N37</f>
+        <v/>
+      </c>
+      <c r="P33" s="39">
+        <f>O37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + CPI Indexation</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D34" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E34" s="26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F34" s="26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G34" s="39">
+        <f>G33*Assumptions!G15</f>
+        <v/>
+      </c>
+      <c r="H34" s="39">
+        <f>H33*Assumptions!H15</f>
+        <v/>
+      </c>
+      <c r="I34" s="39">
+        <f>I33*Assumptions!I15</f>
+        <v/>
+      </c>
+      <c r="J34" s="39">
+        <f>J33*Assumptions!J15</f>
+        <v/>
+      </c>
+      <c r="K34" s="39">
+        <f>K33*Assumptions!K15</f>
+        <v/>
+      </c>
+      <c r="L34" s="39">
+        <f>L33*Assumptions!L15</f>
+        <v/>
+      </c>
+      <c r="M34" s="39">
+        <f>M33*Assumptions!M15</f>
+        <v/>
+      </c>
+      <c r="N34" s="39">
+        <f>N33*Assumptions!N15</f>
+        <v/>
+      </c>
+      <c r="O34" s="39">
+        <f>O33*Assumptions!O15</f>
+        <v/>
+      </c>
+      <c r="P34" s="39">
+        <f>P33*Assumptions!P15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    + Capex Additions (×3% allocation)</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E35" s="26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F35" s="26" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G35" s="39">
+        <f>'Fixed Assets'!G39</f>
+        <v/>
+      </c>
+      <c r="H35" s="39">
+        <f>'Fixed Assets'!H39</f>
+        <v/>
+      </c>
+      <c r="I35" s="39">
+        <f>'Fixed Assets'!I39</f>
+        <v/>
+      </c>
+      <c r="J35" s="39">
+        <f>'Fixed Assets'!J39</f>
+        <v/>
+      </c>
+      <c r="K35" s="39">
+        <f>'Fixed Assets'!K39</f>
+        <v/>
+      </c>
+      <c r="L35" s="39">
+        <f>'Fixed Assets'!L39</f>
+        <v/>
+      </c>
+      <c r="M35" s="39">
+        <f>'Fixed Assets'!M39</f>
+        <v/>
+      </c>
+      <c r="N35" s="39">
+        <f>'Fixed Assets'!N39</f>
+        <v/>
+      </c>
+      <c r="O35" s="39">
+        <f>'Fixed Assets'!O39</f>
+        <v/>
+      </c>
+      <c r="P35" s="39">
+        <f>'Fixed Assets'!P39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    − Regulatory Depreciation  (÷ 30 yr AER life)</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E36" s="26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F36" s="26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G36" s="39">
+        <f>G33/30</f>
+        <v/>
+      </c>
+      <c r="H36" s="39">
+        <f>H33/30</f>
+        <v/>
+      </c>
+      <c r="I36" s="39">
+        <f>I33/30</f>
+        <v/>
+      </c>
+      <c r="J36" s="39">
+        <f>J33/30</f>
+        <v/>
+      </c>
+      <c r="K36" s="39">
+        <f>K33/30</f>
+        <v/>
+      </c>
+      <c r="L36" s="39">
+        <f>L33/30</f>
+        <v/>
+      </c>
+      <c r="M36" s="39">
+        <f>M33/30</f>
+        <v/>
+      </c>
+      <c r="N36" s="39">
+        <f>N33/30</f>
+        <v/>
+      </c>
+      <c r="O36" s="39">
+        <f>O33/30</f>
+        <v/>
+      </c>
+      <c r="P36" s="39">
+        <f>P33/30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    = Closing RAB</t>
+        </is>
+      </c>
+      <c r="B37" s="43" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="C37" s="43" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="D37" s="43" t="n">
+        <v>164</v>
+      </c>
+      <c r="E37" s="43" t="n">
+        <v>174.1</v>
+      </c>
+      <c r="F37" s="43" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="G37" s="44">
+        <f>G33+G34+G35-G36</f>
+        <v/>
+      </c>
+      <c r="H37" s="44">
+        <f>H33+H34+H35-H36</f>
+        <v/>
+      </c>
+      <c r="I37" s="44">
+        <f>I33+I34+I35-I36</f>
+        <v/>
+      </c>
+      <c r="J37" s="44">
+        <f>J33+J34+J35-J36</f>
+        <v/>
+      </c>
+      <c r="K37" s="44">
+        <f>K33+K34+K35-K36</f>
+        <v/>
+      </c>
+      <c r="L37" s="44">
+        <f>L33+L34+L35-L36</f>
+        <v/>
+      </c>
+      <c r="M37" s="44">
+        <f>M33+M34+M35-M36</f>
+        <v/>
+      </c>
+      <c r="N37" s="44">
+        <f>N33+N34+N35-N36</f>
+        <v/>
+      </c>
+      <c r="O37" s="44">
+        <f>O33+O34+O35-O36</f>
+        <v/>
+      </c>
+      <c r="P37" s="44">
+        <f>P33+P34+P35-P36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL REGULATORY ASSET BASE ($M)</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="16" t="n"/>
+      <c r="H39" s="16" t="n"/>
+      <c r="I39" s="16" t="n"/>
+      <c r="J39" s="16" t="n"/>
+      <c r="K39" s="16" t="n"/>
+      <c r="L39" s="16" t="n"/>
+      <c r="M39" s="16" t="n"/>
+      <c r="N39" s="16" t="n"/>
+      <c r="O39" s="16" t="n"/>
+      <c r="P39" s="16" t="n"/>
+      <c r="Q39" s="16" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total Opening RAB</t>
+        </is>
+      </c>
+      <c r="B40" s="26">
+        <f>B5+B12+B19+B26+B33</f>
+        <v/>
+      </c>
+      <c r="C40" s="26">
+        <f>C5+C12+C19+C26+C33</f>
+        <v/>
+      </c>
+      <c r="D40" s="26">
+        <f>D5+D12+D19+D26+D33</f>
+        <v/>
+      </c>
+      <c r="E40" s="26">
+        <f>E5+E12+E19+E26+E33</f>
+        <v/>
+      </c>
+      <c r="F40" s="26">
+        <f>F5+F12+F19+F26+F33</f>
+        <v/>
+      </c>
+      <c r="G40" s="39">
+        <f>G5+G12+G19+G26+G33</f>
+        <v/>
+      </c>
+      <c r="H40" s="39">
+        <f>H5+H12+H19+H26+H33</f>
+        <v/>
+      </c>
+      <c r="I40" s="39">
+        <f>I5+I12+I19+I26+I33</f>
+        <v/>
+      </c>
+      <c r="J40" s="39">
+        <f>J5+J12+J19+J26+J33</f>
+        <v/>
+      </c>
+      <c r="K40" s="39">
+        <f>K5+K12+K19+K26+K33</f>
+        <v/>
+      </c>
+      <c r="L40" s="39">
+        <f>L5+L12+L19+L26+L33</f>
+        <v/>
+      </c>
+      <c r="M40" s="39">
+        <f>M5+M12+M19+M26+M33</f>
+        <v/>
+      </c>
+      <c r="N40" s="39">
+        <f>N5+N12+N19+N26+N33</f>
+        <v/>
+      </c>
+      <c r="O40" s="39">
+        <f>O5+O12+O19+O26+O33</f>
+        <v/>
+      </c>
+      <c r="P40" s="39">
+        <f>P5+P12+P19+P26+P33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total CPI Indexation</t>
+        </is>
+      </c>
+      <c r="B41" s="26">
+        <f>B6+B13+B20+B27+B34</f>
+        <v/>
+      </c>
+      <c r="C41" s="26">
+        <f>C6+C13+C20+C27+C34</f>
+        <v/>
+      </c>
+      <c r="D41" s="26">
+        <f>D6+D13+D20+D27+D34</f>
+        <v/>
+      </c>
+      <c r="E41" s="26">
+        <f>E6+E13+E20+E27+E34</f>
+        <v/>
+      </c>
+      <c r="F41" s="26">
+        <f>F6+F13+F20+F27+F34</f>
+        <v/>
+      </c>
+      <c r="G41" s="39">
+        <f>G6+G13+G20+G27+G34</f>
+        <v/>
+      </c>
+      <c r="H41" s="39">
+        <f>H6+H13+H20+H27+H34</f>
+        <v/>
+      </c>
+      <c r="I41" s="39">
+        <f>I6+I13+I20+I27+I34</f>
+        <v/>
+      </c>
+      <c r="J41" s="39">
+        <f>J6+J13+J20+J27+J34</f>
+        <v/>
+      </c>
+      <c r="K41" s="39">
+        <f>K6+K13+K20+K27+K34</f>
+        <v/>
+      </c>
+      <c r="L41" s="39">
+        <f>L6+L13+L20+L27+L34</f>
+        <v/>
+      </c>
+      <c r="M41" s="39">
+        <f>M6+M13+M20+M27+M34</f>
+        <v/>
+      </c>
+      <c r="N41" s="39">
+        <f>N6+N13+N20+N27+N34</f>
+        <v/>
+      </c>
+      <c r="O41" s="39">
+        <f>O6+O13+O20+O27+O34</f>
+        <v/>
+      </c>
+      <c r="P41" s="39">
+        <f>P6+P13+P20+P27+P34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total Capex Additions</t>
+        </is>
+      </c>
+      <c r="B42" s="26">
+        <f>B7+B14+B21+B28+B35</f>
+        <v/>
+      </c>
+      <c r="C42" s="26">
+        <f>C7+C14+C21+C28+C35</f>
+        <v/>
+      </c>
+      <c r="D42" s="26">
+        <f>D7+D14+D21+D28+D35</f>
+        <v/>
+      </c>
+      <c r="E42" s="26">
+        <f>E7+E14+E21+E28+E35</f>
+        <v/>
+      </c>
+      <c r="F42" s="26">
+        <f>F7+F14+F21+F28+F35</f>
+        <v/>
+      </c>
+      <c r="G42" s="39">
+        <f>G7+G14+G21+G28+G35</f>
+        <v/>
+      </c>
+      <c r="H42" s="39">
+        <f>H7+H14+H21+H28+H35</f>
+        <v/>
+      </c>
+      <c r="I42" s="39">
+        <f>I7+I14+I21+I28+I35</f>
+        <v/>
+      </c>
+      <c r="J42" s="39">
+        <f>J7+J14+J21+J28+J35</f>
+        <v/>
+      </c>
+      <c r="K42" s="39">
+        <f>K7+K14+K21+K28+K35</f>
+        <v/>
+      </c>
+      <c r="L42" s="39">
+        <f>L7+L14+L21+L28+L35</f>
+        <v/>
+      </c>
+      <c r="M42" s="39">
+        <f>M7+M14+M21+M28+M35</f>
+        <v/>
+      </c>
+      <c r="N42" s="39">
+        <f>N7+N14+N21+N28+N35</f>
+        <v/>
+      </c>
+      <c r="O42" s="39">
+        <f>O7+O14+O21+O28+O35</f>
+        <v/>
+      </c>
+      <c r="P42" s="39">
+        <f>P7+P14+P21+P28+P35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total Regulatory Depreciation  →  Return of RAB (PTRM)</t>
+        </is>
+      </c>
+      <c r="B43" s="26">
+        <f>B8+B15+B22+B29+B36</f>
+        <v/>
+      </c>
+      <c r="C43" s="26">
+        <f>C8+C15+C22+C29+C36</f>
+        <v/>
+      </c>
+      <c r="D43" s="26">
+        <f>D8+D15+D22+D29+D36</f>
+        <v/>
+      </c>
+      <c r="E43" s="26">
+        <f>E8+E15+E22+E29+E36</f>
+        <v/>
+      </c>
+      <c r="F43" s="26">
+        <f>F8+F15+F22+F29+F36</f>
+        <v/>
+      </c>
+      <c r="G43" s="39">
+        <f>G8+G15+G22+G29+G36</f>
+        <v/>
+      </c>
+      <c r="H43" s="39">
+        <f>H8+H15+H22+H29+H36</f>
+        <v/>
+      </c>
+      <c r="I43" s="39">
+        <f>I8+I15+I22+I29+I36</f>
+        <v/>
+      </c>
+      <c r="J43" s="39">
+        <f>J8+J15+J22+J29+J36</f>
+        <v/>
+      </c>
+      <c r="K43" s="39">
+        <f>K8+K15+K22+K29+K36</f>
+        <v/>
+      </c>
+      <c r="L43" s="39">
+        <f>L8+L15+L22+L29+L36</f>
+        <v/>
+      </c>
+      <c r="M43" s="39">
+        <f>M8+M15+M22+M29+M36</f>
+        <v/>
+      </c>
+      <c r="N43" s="39">
+        <f>N8+N15+N22+N29+N36</f>
+        <v/>
+      </c>
+      <c r="O43" s="39">
+        <f>O8+O15+O22+O29+O36</f>
+        <v/>
+      </c>
+      <c r="P43" s="39">
+        <f>P8+P15+P22+P29+P36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total Closing RAB</t>
+        </is>
+      </c>
+      <c r="B44" s="44">
+        <f>B9+B16+B23+B30+B37</f>
+        <v/>
+      </c>
+      <c r="C44" s="44">
+        <f>C9+C16+C23+C30+C37</f>
+        <v/>
+      </c>
+      <c r="D44" s="44">
+        <f>D9+D16+D23+D30+D37</f>
+        <v/>
+      </c>
+      <c r="E44" s="44">
+        <f>E9+E16+E23+E30+E37</f>
+        <v/>
+      </c>
+      <c r="F44" s="44">
+        <f>F9+F16+F23+F30+F37</f>
+        <v/>
+      </c>
+      <c r="G44" s="44">
+        <f>G9+G16+G23+G30+G37</f>
+        <v/>
+      </c>
+      <c r="H44" s="44">
+        <f>H9+H16+H23+H30+H37</f>
+        <v/>
+      </c>
+      <c r="I44" s="44">
+        <f>I9+I16+I23+I30+I37</f>
+        <v/>
+      </c>
+      <c r="J44" s="44">
+        <f>J9+J16+J23+J30+J37</f>
+        <v/>
+      </c>
+      <c r="K44" s="44">
+        <f>K9+K16+K23+K30+K37</f>
+        <v/>
+      </c>
+      <c r="L44" s="44">
+        <f>L9+L16+L23+L30+L37</f>
+        <v/>
+      </c>
+      <c r="M44" s="44">
+        <f>M9+M16+M23+M30+M37</f>
+        <v/>
+      </c>
+      <c r="N44" s="44">
+        <f>N9+N16+N23+N30+N37</f>
+        <v/>
+      </c>
+      <c r="O44" s="44">
+        <f>O9+O16+O23+O30+O37</f>
+        <v/>
+      </c>
+      <c r="P44" s="44">
+        <f>P9+P16+P23+P30+P37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Average RAB  [(Opening + Closing) ÷ 2]  →  Return on RAB base (PTRM)</t>
+        </is>
+      </c>
+      <c r="B46" s="26">
+        <f>(B40+B44)/2</f>
+        <v/>
+      </c>
+      <c r="C46" s="26">
+        <f>(C40+C44)/2</f>
+        <v/>
+      </c>
+      <c r="D46" s="26">
+        <f>(D40+D44)/2</f>
+        <v/>
+      </c>
+      <c r="E46" s="26">
+        <f>(E40+E44)/2</f>
+        <v/>
+      </c>
+      <c r="F46" s="26">
+        <f>(F40+F44)/2</f>
+        <v/>
+      </c>
+      <c r="G46" s="39">
+        <f>(G40+G44)/2</f>
+        <v/>
+      </c>
+      <c r="H46" s="39">
+        <f>(H40+H44)/2</f>
+        <v/>
+      </c>
+      <c r="I46" s="39">
+        <f>(I40+I44)/2</f>
+        <v/>
+      </c>
+      <c r="J46" s="39">
+        <f>(J40+J44)/2</f>
+        <v/>
+      </c>
+      <c r="K46" s="39">
+        <f>(K40+K44)/2</f>
+        <v/>
+      </c>
+      <c r="L46" s="39">
+        <f>(L40+L44)/2</f>
+        <v/>
+      </c>
+      <c r="M46" s="39">
+        <f>(M40+M44)/2</f>
+        <v/>
+      </c>
+      <c r="N46" s="39">
+        <f>(N40+N44)/2</f>
+        <v/>
+      </c>
+      <c r="O46" s="39">
+        <f>(O40+O44)/2</f>
+        <v/>
+      </c>
+      <c r="P46" s="39">
+        <f>(P40+P44)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Accumulated Regulatory Depreciation ($M)</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="16" t="n"/>
+      <c r="G48" s="16" t="n"/>
+      <c r="H48" s="16" t="n"/>
+      <c r="I48" s="16" t="n"/>
+      <c r="J48" s="16" t="n"/>
+      <c r="K48" s="16" t="n"/>
+      <c r="L48" s="16" t="n"/>
+      <c r="M48" s="16" t="n"/>
+      <c r="N48" s="16" t="n"/>
+      <c r="O48" s="16" t="n"/>
+      <c r="P48" s="16" t="n"/>
+      <c r="Q48" s="16" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening Accumulated Reg. Dep.</t>
+        </is>
+      </c>
+      <c r="B49" s="26">
+        <f>Assumptions!$B$36</f>
+        <v/>
+      </c>
+      <c r="C49" s="26">
+        <f>B51</f>
+        <v/>
+      </c>
+      <c r="D49" s="26">
+        <f>C51</f>
+        <v/>
+      </c>
+      <c r="E49" s="26">
+        <f>D51</f>
+        <v/>
+      </c>
+      <c r="F49" s="26">
+        <f>E51</f>
+        <v/>
+      </c>
+      <c r="G49" s="39">
+        <f>F51</f>
+        <v/>
+      </c>
+      <c r="H49" s="39">
+        <f>G51</f>
+        <v/>
+      </c>
+      <c r="I49" s="39">
+        <f>H51</f>
+        <v/>
+      </c>
+      <c r="J49" s="39">
+        <f>I51</f>
+        <v/>
+      </c>
+      <c r="K49" s="39">
+        <f>J51</f>
+        <v/>
+      </c>
+      <c r="L49" s="39">
+        <f>K51</f>
+        <v/>
+      </c>
+      <c r="M49" s="39">
+        <f>L51</f>
+        <v/>
+      </c>
+      <c r="N49" s="39">
+        <f>M51</f>
+        <v/>
+      </c>
+      <c r="O49" s="39">
+        <f>N51</f>
+        <v/>
+      </c>
+      <c r="P49" s="39">
+        <f>O51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Current Year Reg. Dep.</t>
+        </is>
+      </c>
+      <c r="B50" s="26">
+        <f>B43</f>
+        <v/>
+      </c>
+      <c r="C50" s="26">
+        <f>C43</f>
+        <v/>
+      </c>
+      <c r="D50" s="26">
+        <f>D43</f>
+        <v/>
+      </c>
+      <c r="E50" s="26">
+        <f>E43</f>
+        <v/>
+      </c>
+      <c r="F50" s="26">
+        <f>F43</f>
+        <v/>
+      </c>
+      <c r="G50" s="39">
+        <f>G43</f>
+        <v/>
+      </c>
+      <c r="H50" s="39">
+        <f>H43</f>
+        <v/>
+      </c>
+      <c r="I50" s="39">
+        <f>I43</f>
+        <v/>
+      </c>
+      <c r="J50" s="39">
+        <f>J43</f>
+        <v/>
+      </c>
+      <c r="K50" s="39">
+        <f>K43</f>
+        <v/>
+      </c>
+      <c r="L50" s="39">
+        <f>L43</f>
+        <v/>
+      </c>
+      <c r="M50" s="39">
+        <f>M43</f>
+        <v/>
+      </c>
+      <c r="N50" s="39">
+        <f>N43</f>
+        <v/>
+      </c>
+      <c r="O50" s="39">
+        <f>O43</f>
+        <v/>
+      </c>
+      <c r="P50" s="39">
+        <f>P43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Closing Accumulated Reg. Dep.</t>
+        </is>
+      </c>
+      <c r="B51" s="44">
+        <f>B49+B50</f>
+        <v/>
+      </c>
+      <c r="C51" s="44">
+        <f>C49+C50</f>
+        <v/>
+      </c>
+      <c r="D51" s="44">
+        <f>D49+D50</f>
+        <v/>
+      </c>
+      <c r="E51" s="44">
+        <f>E49+E50</f>
+        <v/>
+      </c>
+      <c r="F51" s="44">
+        <f>F49+F50</f>
+        <v/>
+      </c>
+      <c r="G51" s="44">
+        <f>G49+G50</f>
+        <v/>
+      </c>
+      <c r="H51" s="44">
+        <f>H49+H50</f>
+        <v/>
+      </c>
+      <c r="I51" s="44">
+        <f>I49+I50</f>
+        <v/>
+      </c>
+      <c r="J51" s="44">
+        <f>J49+J50</f>
+        <v/>
+      </c>
+      <c r="K51" s="44">
+        <f>K49+K50</f>
+        <v/>
+      </c>
+      <c r="L51" s="44">
+        <f>L49+L50</f>
+        <v/>
+      </c>
+      <c r="M51" s="44">
+        <f>M49+M50</f>
+        <v/>
+      </c>
+      <c r="N51" s="44">
+        <f>N49+N50</f>
+        <v/>
+      </c>
+      <c r="O51" s="44">
+        <f>O49+O50</f>
+        <v/>
+      </c>
+      <c r="P51" s="44">
+        <f>P49+P50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Regulatory Period Summaries</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="n"/>
+      <c r="C53" s="16" t="n"/>
+      <c r="D53" s="16" t="n"/>
+      <c r="E53" s="16" t="n"/>
+      <c r="F53" s="16" t="n"/>
+      <c r="G53" s="16" t="n"/>
+      <c r="H53" s="16" t="n"/>
+      <c r="I53" s="16" t="n"/>
+      <c r="J53" s="16" t="n"/>
+      <c r="K53" s="16" t="n"/>
+      <c r="L53" s="16" t="n"/>
+      <c r="M53" s="16" t="n"/>
+      <c r="N53" s="16" t="n"/>
+      <c r="O53" s="16" t="n"/>
+      <c r="P53" s="16" t="n"/>
+      <c r="Q53" s="16" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RCP1 (FY2024–28)  Total Capex ($M)</t>
+        </is>
+      </c>
+      <c r="B54" s="46">
+        <f>G42+H42+I42+J42+K42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RCP1 (FY2024–28)  Total Reg. Depreciation</t>
+        </is>
+      </c>
+      <c r="B55" s="46">
+        <f>G43+H43+I43+J43+K43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RCP1 (FY2024–28)  Average Closing RAB</t>
+        </is>
+      </c>
+      <c r="B56" s="46">
+        <f>G44+H44+I44+J44+K44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RCP2 (FY2029–33)  Total Capex ($M)</t>
+        </is>
+      </c>
+      <c r="B58" s="46">
+        <f>L42+M42+N42+O42+P42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RCP2 (FY2029–33)  Total Reg. Depreciation</t>
+        </is>
+      </c>
+      <c r="B59" s="46">
+        <f>L43+M43+N43+O43+P43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RCP2 (FY2029–33)  Average Closing RAB</t>
+        </is>
+      </c>
+      <c r="B60" s="46">
+        <f>L44+M44+N44+O44+P44</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3170,7 +5712,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="56" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>POST TAX REVENUE MODEL (PTRM) — Maximum Allowed Revenue</t>
         </is>
@@ -3871,7 +6413,2300 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004B0082"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="56" t="inlineStr">
+        <is>
+          <t>AER DEPRECIATION TRACKING MODEL — Regulatory | Accounting | Tax (ATO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>$AUD Millions</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>FY2019A</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>FY2020A</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>FY2021A</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>FY2022A</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>FY2023A</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>FY2024E</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>FY2025E</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="M2" s="14" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="N2" s="14" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="O2" s="14" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="P2" s="14" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>SECTION A — Regulatory Depreciation (AER Standard Lives) ($M)</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="n"/>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="16" t="n"/>
+      <c r="K4" s="16" t="n"/>
+      <c r="L4" s="16" t="n"/>
+      <c r="M4" s="16" t="n"/>
+      <c r="N4" s="16" t="n"/>
+      <c r="O4" s="16" t="n"/>
+      <c r="P4" s="16" t="n"/>
+      <c r="Q4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Transmission Lines  (÷60yr AER)</t>
+        </is>
+      </c>
+      <c r="B5" s="26">
+        <f>'RAB Roll-Forward'!B8</f>
+        <v/>
+      </c>
+      <c r="C5" s="26">
+        <f>'RAB Roll-Forward'!C8</f>
+        <v/>
+      </c>
+      <c r="D5" s="26">
+        <f>'RAB Roll-Forward'!D8</f>
+        <v/>
+      </c>
+      <c r="E5" s="26">
+        <f>'RAB Roll-Forward'!E8</f>
+        <v/>
+      </c>
+      <c r="F5" s="26">
+        <f>'RAB Roll-Forward'!F8</f>
+        <v/>
+      </c>
+      <c r="G5" s="39">
+        <f>'RAB Roll-Forward'!G8</f>
+        <v/>
+      </c>
+      <c r="H5" s="39">
+        <f>'RAB Roll-Forward'!H8</f>
+        <v/>
+      </c>
+      <c r="I5" s="39">
+        <f>'RAB Roll-Forward'!I8</f>
+        <v/>
+      </c>
+      <c r="J5" s="39">
+        <f>'RAB Roll-Forward'!J8</f>
+        <v/>
+      </c>
+      <c r="K5" s="39">
+        <f>'RAB Roll-Forward'!K8</f>
+        <v/>
+      </c>
+      <c r="L5" s="39">
+        <f>'RAB Roll-Forward'!L8</f>
+        <v/>
+      </c>
+      <c r="M5" s="39">
+        <f>'RAB Roll-Forward'!M8</f>
+        <v/>
+      </c>
+      <c r="N5" s="39">
+        <f>'RAB Roll-Forward'!N8</f>
+        <v/>
+      </c>
+      <c r="O5" s="39">
+        <f>'RAB Roll-Forward'!O8</f>
+        <v/>
+      </c>
+      <c r="P5" s="39">
+        <f>'RAB Roll-Forward'!P8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Substations  (÷55yr AER)</t>
+        </is>
+      </c>
+      <c r="B6" s="26">
+        <f>'RAB Roll-Forward'!B15</f>
+        <v/>
+      </c>
+      <c r="C6" s="26">
+        <f>'RAB Roll-Forward'!C15</f>
+        <v/>
+      </c>
+      <c r="D6" s="26">
+        <f>'RAB Roll-Forward'!D15</f>
+        <v/>
+      </c>
+      <c r="E6" s="26">
+        <f>'RAB Roll-Forward'!E15</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>'RAB Roll-Forward'!F15</f>
+        <v/>
+      </c>
+      <c r="G6" s="39">
+        <f>'RAB Roll-Forward'!G15</f>
+        <v/>
+      </c>
+      <c r="H6" s="39">
+        <f>'RAB Roll-Forward'!H15</f>
+        <v/>
+      </c>
+      <c r="I6" s="39">
+        <f>'RAB Roll-Forward'!I15</f>
+        <v/>
+      </c>
+      <c r="J6" s="39">
+        <f>'RAB Roll-Forward'!J15</f>
+        <v/>
+      </c>
+      <c r="K6" s="39">
+        <f>'RAB Roll-Forward'!K15</f>
+        <v/>
+      </c>
+      <c r="L6" s="39">
+        <f>'RAB Roll-Forward'!L15</f>
+        <v/>
+      </c>
+      <c r="M6" s="39">
+        <f>'RAB Roll-Forward'!M15</f>
+        <v/>
+      </c>
+      <c r="N6" s="39">
+        <f>'RAB Roll-Forward'!N15</f>
+        <v/>
+      </c>
+      <c r="O6" s="39">
+        <f>'RAB Roll-Forward'!O15</f>
+        <v/>
+      </c>
+      <c r="P6" s="39">
+        <f>'RAB Roll-Forward'!P15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Transformers  (÷45yr AER)</t>
+        </is>
+      </c>
+      <c r="B7" s="26">
+        <f>'RAB Roll-Forward'!B22</f>
+        <v/>
+      </c>
+      <c r="C7" s="26">
+        <f>'RAB Roll-Forward'!C22</f>
+        <v/>
+      </c>
+      <c r="D7" s="26">
+        <f>'RAB Roll-Forward'!D22</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>'RAB Roll-Forward'!E22</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>'RAB Roll-Forward'!F22</f>
+        <v/>
+      </c>
+      <c r="G7" s="39">
+        <f>'RAB Roll-Forward'!G22</f>
+        <v/>
+      </c>
+      <c r="H7" s="39">
+        <f>'RAB Roll-Forward'!H22</f>
+        <v/>
+      </c>
+      <c r="I7" s="39">
+        <f>'RAB Roll-Forward'!I22</f>
+        <v/>
+      </c>
+      <c r="J7" s="39">
+        <f>'RAB Roll-Forward'!J22</f>
+        <v/>
+      </c>
+      <c r="K7" s="39">
+        <f>'RAB Roll-Forward'!K22</f>
+        <v/>
+      </c>
+      <c r="L7" s="39">
+        <f>'RAB Roll-Forward'!L22</f>
+        <v/>
+      </c>
+      <c r="M7" s="39">
+        <f>'RAB Roll-Forward'!M22</f>
+        <v/>
+      </c>
+      <c r="N7" s="39">
+        <f>'RAB Roll-Forward'!N22</f>
+        <v/>
+      </c>
+      <c r="O7" s="39">
+        <f>'RAB Roll-Forward'!O22</f>
+        <v/>
+      </c>
+      <c r="P7" s="39">
+        <f>'RAB Roll-Forward'!P22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SCADA &amp; Control  (÷25yr AER)</t>
+        </is>
+      </c>
+      <c r="B8" s="26">
+        <f>'RAB Roll-Forward'!B29</f>
+        <v/>
+      </c>
+      <c r="C8" s="26">
+        <f>'RAB Roll-Forward'!C29</f>
+        <v/>
+      </c>
+      <c r="D8" s="26">
+        <f>'RAB Roll-Forward'!D29</f>
+        <v/>
+      </c>
+      <c r="E8" s="26">
+        <f>'RAB Roll-Forward'!E29</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>'RAB Roll-Forward'!F29</f>
+        <v/>
+      </c>
+      <c r="G8" s="39">
+        <f>'RAB Roll-Forward'!G29</f>
+        <v/>
+      </c>
+      <c r="H8" s="39">
+        <f>'RAB Roll-Forward'!H29</f>
+        <v/>
+      </c>
+      <c r="I8" s="39">
+        <f>'RAB Roll-Forward'!I29</f>
+        <v/>
+      </c>
+      <c r="J8" s="39">
+        <f>'RAB Roll-Forward'!J29</f>
+        <v/>
+      </c>
+      <c r="K8" s="39">
+        <f>'RAB Roll-Forward'!K29</f>
+        <v/>
+      </c>
+      <c r="L8" s="39">
+        <f>'RAB Roll-Forward'!L29</f>
+        <v/>
+      </c>
+      <c r="M8" s="39">
+        <f>'RAB Roll-Forward'!M29</f>
+        <v/>
+      </c>
+      <c r="N8" s="39">
+        <f>'RAB Roll-Forward'!N29</f>
+        <v/>
+      </c>
+      <c r="O8" s="39">
+        <f>'RAB Roll-Forward'!O29</f>
+        <v/>
+      </c>
+      <c r="P8" s="39">
+        <f>'RAB Roll-Forward'!P29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other Equipment  (÷30yr AER)</t>
+        </is>
+      </c>
+      <c r="B9" s="26">
+        <f>'RAB Roll-Forward'!B36</f>
+        <v/>
+      </c>
+      <c r="C9" s="26">
+        <f>'RAB Roll-Forward'!C36</f>
+        <v/>
+      </c>
+      <c r="D9" s="26">
+        <f>'RAB Roll-Forward'!D36</f>
+        <v/>
+      </c>
+      <c r="E9" s="26">
+        <f>'RAB Roll-Forward'!E36</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>'RAB Roll-Forward'!F36</f>
+        <v/>
+      </c>
+      <c r="G9" s="39">
+        <f>'RAB Roll-Forward'!G36</f>
+        <v/>
+      </c>
+      <c r="H9" s="39">
+        <f>'RAB Roll-Forward'!H36</f>
+        <v/>
+      </c>
+      <c r="I9" s="39">
+        <f>'RAB Roll-Forward'!I36</f>
+        <v/>
+      </c>
+      <c r="J9" s="39">
+        <f>'RAB Roll-Forward'!J36</f>
+        <v/>
+      </c>
+      <c r="K9" s="39">
+        <f>'RAB Roll-Forward'!K36</f>
+        <v/>
+      </c>
+      <c r="L9" s="39">
+        <f>'RAB Roll-Forward'!L36</f>
+        <v/>
+      </c>
+      <c r="M9" s="39">
+        <f>'RAB Roll-Forward'!M36</f>
+        <v/>
+      </c>
+      <c r="N9" s="39">
+        <f>'RAB Roll-Forward'!N36</f>
+        <v/>
+      </c>
+      <c r="O9" s="39">
+        <f>'RAB Roll-Forward'!O36</f>
+        <v/>
+      </c>
+      <c r="P9" s="39">
+        <f>'RAB Roll-Forward'!P36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total Regulatory Depreciation  →  Return of RAB (PTRM)</t>
+        </is>
+      </c>
+      <c r="B10" s="44">
+        <f>SUM(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="44">
+        <f>SUM(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="44">
+        <f>SUM(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="44">
+        <f>SUM(E5:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="44">
+        <f>SUM(F5:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="44">
+        <f>SUM(G5:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="44">
+        <f>SUM(H5:H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="44">
+        <f>SUM(I5:I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="44">
+        <f>SUM(J5:J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="44">
+        <f>SUM(K5:K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="44">
+        <f>SUM(L5:L9)</f>
+        <v/>
+      </c>
+      <c r="M10" s="44">
+        <f>SUM(M5:M9)</f>
+        <v/>
+      </c>
+      <c r="N10" s="44">
+        <f>SUM(N5:N9)</f>
+        <v/>
+      </c>
+      <c r="O10" s="44">
+        <f>SUM(O5:O9)</f>
+        <v/>
+      </c>
+      <c r="P10" s="44">
+        <f>SUM(P5:P9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>SECTION B — Accounting Depreciation AASB 116 (from Fixed Assets tab) ($M)</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="16" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n"/>
+      <c r="P12" s="16" t="n"/>
+      <c r="Q12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Transmission Lines  (÷40yr acc.)</t>
+        </is>
+      </c>
+      <c r="B13" s="26">
+        <f>'Fixed Assets'!B11</f>
+        <v/>
+      </c>
+      <c r="C13" s="26">
+        <f>'Fixed Assets'!C11</f>
+        <v/>
+      </c>
+      <c r="D13" s="26">
+        <f>'Fixed Assets'!D11</f>
+        <v/>
+      </c>
+      <c r="E13" s="26">
+        <f>'Fixed Assets'!E11</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>'Fixed Assets'!F11</f>
+        <v/>
+      </c>
+      <c r="G13" s="39">
+        <f>'Fixed Assets'!G11</f>
+        <v/>
+      </c>
+      <c r="H13" s="39">
+        <f>'Fixed Assets'!H11</f>
+        <v/>
+      </c>
+      <c r="I13" s="39">
+        <f>'Fixed Assets'!I11</f>
+        <v/>
+      </c>
+      <c r="J13" s="39">
+        <f>'Fixed Assets'!J11</f>
+        <v/>
+      </c>
+      <c r="K13" s="39">
+        <f>'Fixed Assets'!K11</f>
+        <v/>
+      </c>
+      <c r="L13" s="39">
+        <f>'Fixed Assets'!L11</f>
+        <v/>
+      </c>
+      <c r="M13" s="39">
+        <f>'Fixed Assets'!M11</f>
+        <v/>
+      </c>
+      <c r="N13" s="39">
+        <f>'Fixed Assets'!N11</f>
+        <v/>
+      </c>
+      <c r="O13" s="39">
+        <f>'Fixed Assets'!O11</f>
+        <v/>
+      </c>
+      <c r="P13" s="39">
+        <f>'Fixed Assets'!P11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Substations  (÷40yr acc.)</t>
+        </is>
+      </c>
+      <c r="B14" s="26">
+        <f>'Fixed Assets'!B19</f>
+        <v/>
+      </c>
+      <c r="C14" s="26">
+        <f>'Fixed Assets'!C19</f>
+        <v/>
+      </c>
+      <c r="D14" s="26">
+        <f>'Fixed Assets'!D19</f>
+        <v/>
+      </c>
+      <c r="E14" s="26">
+        <f>'Fixed Assets'!E19</f>
+        <v/>
+      </c>
+      <c r="F14" s="26">
+        <f>'Fixed Assets'!F19</f>
+        <v/>
+      </c>
+      <c r="G14" s="39">
+        <f>'Fixed Assets'!G19</f>
+        <v/>
+      </c>
+      <c r="H14" s="39">
+        <f>'Fixed Assets'!H19</f>
+        <v/>
+      </c>
+      <c r="I14" s="39">
+        <f>'Fixed Assets'!I19</f>
+        <v/>
+      </c>
+      <c r="J14" s="39">
+        <f>'Fixed Assets'!J19</f>
+        <v/>
+      </c>
+      <c r="K14" s="39">
+        <f>'Fixed Assets'!K19</f>
+        <v/>
+      </c>
+      <c r="L14" s="39">
+        <f>'Fixed Assets'!L19</f>
+        <v/>
+      </c>
+      <c r="M14" s="39">
+        <f>'Fixed Assets'!M19</f>
+        <v/>
+      </c>
+      <c r="N14" s="39">
+        <f>'Fixed Assets'!N19</f>
+        <v/>
+      </c>
+      <c r="O14" s="39">
+        <f>'Fixed Assets'!O19</f>
+        <v/>
+      </c>
+      <c r="P14" s="39">
+        <f>'Fixed Assets'!P19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Transformers  (÷30yr acc.)</t>
+        </is>
+      </c>
+      <c r="B15" s="26">
+        <f>'Fixed Assets'!B27</f>
+        <v/>
+      </c>
+      <c r="C15" s="26">
+        <f>'Fixed Assets'!C27</f>
+        <v/>
+      </c>
+      <c r="D15" s="26">
+        <f>'Fixed Assets'!D27</f>
+        <v/>
+      </c>
+      <c r="E15" s="26">
+        <f>'Fixed Assets'!E27</f>
+        <v/>
+      </c>
+      <c r="F15" s="26">
+        <f>'Fixed Assets'!F27</f>
+        <v/>
+      </c>
+      <c r="G15" s="39">
+        <f>'Fixed Assets'!G27</f>
+        <v/>
+      </c>
+      <c r="H15" s="39">
+        <f>'Fixed Assets'!H27</f>
+        <v/>
+      </c>
+      <c r="I15" s="39">
+        <f>'Fixed Assets'!I27</f>
+        <v/>
+      </c>
+      <c r="J15" s="39">
+        <f>'Fixed Assets'!J27</f>
+        <v/>
+      </c>
+      <c r="K15" s="39">
+        <f>'Fixed Assets'!K27</f>
+        <v/>
+      </c>
+      <c r="L15" s="39">
+        <f>'Fixed Assets'!L27</f>
+        <v/>
+      </c>
+      <c r="M15" s="39">
+        <f>'Fixed Assets'!M27</f>
+        <v/>
+      </c>
+      <c r="N15" s="39">
+        <f>'Fixed Assets'!N27</f>
+        <v/>
+      </c>
+      <c r="O15" s="39">
+        <f>'Fixed Assets'!O27</f>
+        <v/>
+      </c>
+      <c r="P15" s="39">
+        <f>'Fixed Assets'!P27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SCADA &amp; Control  (÷15yr acc.)</t>
+        </is>
+      </c>
+      <c r="B16" s="26">
+        <f>'Fixed Assets'!B35</f>
+        <v/>
+      </c>
+      <c r="C16" s="26">
+        <f>'Fixed Assets'!C35</f>
+        <v/>
+      </c>
+      <c r="D16" s="26">
+        <f>'Fixed Assets'!D35</f>
+        <v/>
+      </c>
+      <c r="E16" s="26">
+        <f>'Fixed Assets'!E35</f>
+        <v/>
+      </c>
+      <c r="F16" s="26">
+        <f>'Fixed Assets'!F35</f>
+        <v/>
+      </c>
+      <c r="G16" s="39">
+        <f>'Fixed Assets'!G35</f>
+        <v/>
+      </c>
+      <c r="H16" s="39">
+        <f>'Fixed Assets'!H35</f>
+        <v/>
+      </c>
+      <c r="I16" s="39">
+        <f>'Fixed Assets'!I35</f>
+        <v/>
+      </c>
+      <c r="J16" s="39">
+        <f>'Fixed Assets'!J35</f>
+        <v/>
+      </c>
+      <c r="K16" s="39">
+        <f>'Fixed Assets'!K35</f>
+        <v/>
+      </c>
+      <c r="L16" s="39">
+        <f>'Fixed Assets'!L35</f>
+        <v/>
+      </c>
+      <c r="M16" s="39">
+        <f>'Fixed Assets'!M35</f>
+        <v/>
+      </c>
+      <c r="N16" s="39">
+        <f>'Fixed Assets'!N35</f>
+        <v/>
+      </c>
+      <c r="O16" s="39">
+        <f>'Fixed Assets'!O35</f>
+        <v/>
+      </c>
+      <c r="P16" s="39">
+        <f>'Fixed Assets'!P35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other Equipment  (÷20yr acc.)</t>
+        </is>
+      </c>
+      <c r="B17" s="26">
+        <f>'Fixed Assets'!B43</f>
+        <v/>
+      </c>
+      <c r="C17" s="26">
+        <f>'Fixed Assets'!C43</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>'Fixed Assets'!D43</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>'Fixed Assets'!E43</f>
+        <v/>
+      </c>
+      <c r="F17" s="26">
+        <f>'Fixed Assets'!F43</f>
+        <v/>
+      </c>
+      <c r="G17" s="39">
+        <f>'Fixed Assets'!G43</f>
+        <v/>
+      </c>
+      <c r="H17" s="39">
+        <f>'Fixed Assets'!H43</f>
+        <v/>
+      </c>
+      <c r="I17" s="39">
+        <f>'Fixed Assets'!I43</f>
+        <v/>
+      </c>
+      <c r="J17" s="39">
+        <f>'Fixed Assets'!J43</f>
+        <v/>
+      </c>
+      <c r="K17" s="39">
+        <f>'Fixed Assets'!K43</f>
+        <v/>
+      </c>
+      <c r="L17" s="39">
+        <f>'Fixed Assets'!L43</f>
+        <v/>
+      </c>
+      <c r="M17" s="39">
+        <f>'Fixed Assets'!M43</f>
+        <v/>
+      </c>
+      <c r="N17" s="39">
+        <f>'Fixed Assets'!N43</f>
+        <v/>
+      </c>
+      <c r="O17" s="39">
+        <f>'Fixed Assets'!O43</f>
+        <v/>
+      </c>
+      <c r="P17" s="39">
+        <f>'Fixed Assets'!P43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total Accounting Depreciation  →  cross-check vs IS D&amp;A charge</t>
+        </is>
+      </c>
+      <c r="B18" s="44">
+        <f>SUM(B13:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="44">
+        <f>SUM(C13:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="44">
+        <f>SUM(D13:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="44">
+        <f>SUM(E13:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="44">
+        <f>SUM(F13:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="44">
+        <f>SUM(G13:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="44">
+        <f>SUM(H13:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="44">
+        <f>SUM(I13:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="44">
+        <f>SUM(J13:J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="44">
+        <f>SUM(K13:K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="44">
+        <f>SUM(L13:L17)</f>
+        <v/>
+      </c>
+      <c r="M18" s="44">
+        <f>SUM(M13:M17)</f>
+        <v/>
+      </c>
+      <c r="N18" s="44">
+        <f>SUM(N13:N17)</f>
+        <v/>
+      </c>
+      <c r="O18" s="44">
+        <f>SUM(O13:O17)</f>
+        <v/>
+      </c>
+      <c r="P18" s="44">
+        <f>SUM(P13:P17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>SECTION C — Depreciation Delta Analysis ($M)</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="16" t="n"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Regulatory Dep − Accounting Dep  (&gt;0 = reg slower → regulatory asset builds)</t>
+        </is>
+      </c>
+      <c r="B21" s="26">
+        <f>B10-B18</f>
+        <v/>
+      </c>
+      <c r="C21" s="26">
+        <f>C10-C18</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>D10-D18</f>
+        <v/>
+      </c>
+      <c r="E21" s="26">
+        <f>E10-E18</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>F10-F18</f>
+        <v/>
+      </c>
+      <c r="G21" s="39">
+        <f>G10-G18</f>
+        <v/>
+      </c>
+      <c r="H21" s="39">
+        <f>H10-H18</f>
+        <v/>
+      </c>
+      <c r="I21" s="39">
+        <f>I10-I18</f>
+        <v/>
+      </c>
+      <c r="J21" s="39">
+        <f>J10-J18</f>
+        <v/>
+      </c>
+      <c r="K21" s="39">
+        <f>K10-K18</f>
+        <v/>
+      </c>
+      <c r="L21" s="39">
+        <f>L10-L18</f>
+        <v/>
+      </c>
+      <c r="M21" s="39">
+        <f>M10-M18</f>
+        <v/>
+      </c>
+      <c r="N21" s="39">
+        <f>N10-N18</f>
+        <v/>
+      </c>
+      <c r="O21" s="39">
+        <f>O10-O18</f>
+        <v/>
+      </c>
+      <c r="P21" s="39">
+        <f>P10-P18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Regulatory Dep − Tax Dep  (&gt;0 = reg slower than ATO → MAR includes more 'Return of RAB')</t>
+        </is>
+      </c>
+      <c r="B22" s="26">
+        <f>B10-B27</f>
+        <v/>
+      </c>
+      <c r="C22" s="26">
+        <f>C10-C27</f>
+        <v/>
+      </c>
+      <c r="D22" s="26">
+        <f>D10-D27</f>
+        <v/>
+      </c>
+      <c r="E22" s="26">
+        <f>E10-E27</f>
+        <v/>
+      </c>
+      <c r="F22" s="26">
+        <f>F10-F27</f>
+        <v/>
+      </c>
+      <c r="G22" s="39">
+        <f>G10-G27</f>
+        <v/>
+      </c>
+      <c r="H22" s="39">
+        <f>H10-H27</f>
+        <v/>
+      </c>
+      <c r="I22" s="39">
+        <f>I10-I27</f>
+        <v/>
+      </c>
+      <c r="J22" s="39">
+        <f>J10-J27</f>
+        <v/>
+      </c>
+      <c r="K22" s="39">
+        <f>K10-K27</f>
+        <v/>
+      </c>
+      <c r="L22" s="39">
+        <f>L10-L27</f>
+        <v/>
+      </c>
+      <c r="M22" s="39">
+        <f>M10-M27</f>
+        <v/>
+      </c>
+      <c r="N22" s="39">
+        <f>N10-N27</f>
+        <v/>
+      </c>
+      <c r="O22" s="39">
+        <f>O10-O27</f>
+        <v/>
+      </c>
+      <c r="P22" s="39">
+        <f>P10-P27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>SECTION D — Tax Asset Base (TAB) Roll-Forward  [ATO Prime Cost | Blended Life: 37 years] ($M)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
+      <c r="J24" s="16" t="n"/>
+      <c r="K24" s="16" t="n"/>
+      <c r="L24" s="16" t="n"/>
+      <c r="M24" s="16" t="n"/>
+      <c r="N24" s="16" t="n"/>
+      <c r="O24" s="16" t="n"/>
+      <c r="P24" s="16" t="n"/>
+      <c r="Q24" s="16" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening TAB</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>3680.9</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>3881.9</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>4102.3</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <v>4341.8</v>
+      </c>
+      <c r="G25" s="39">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="H25" s="39">
+        <f>G28</f>
+        <v/>
+      </c>
+      <c r="I25" s="39">
+        <f>H28</f>
+        <v/>
+      </c>
+      <c r="J25" s="39">
+        <f>I28</f>
+        <v/>
+      </c>
+      <c r="K25" s="39">
+        <f>J28</f>
+        <v/>
+      </c>
+      <c r="L25" s="39">
+        <f>K28</f>
+        <v/>
+      </c>
+      <c r="M25" s="39">
+        <f>L28</f>
+        <v/>
+      </c>
+      <c r="N25" s="39">
+        <f>M28</f>
+        <v/>
+      </c>
+      <c r="O25" s="39">
+        <f>N28</f>
+        <v/>
+      </c>
+      <c r="P25" s="39">
+        <f>O28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Capex Additions  (ATO cost basis)</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>280</v>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>305.1</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>330</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <v>380</v>
+      </c>
+      <c r="G26" s="39">
+        <f>Capex!G13</f>
+        <v/>
+      </c>
+      <c r="H26" s="39">
+        <f>Capex!H13</f>
+        <v/>
+      </c>
+      <c r="I26" s="39">
+        <f>Capex!I13</f>
+        <v/>
+      </c>
+      <c r="J26" s="39">
+        <f>Capex!J13</f>
+        <v/>
+      </c>
+      <c r="K26" s="39">
+        <f>Capex!K13</f>
+        <v/>
+      </c>
+      <c r="L26" s="39">
+        <f>Capex!L13</f>
+        <v/>
+      </c>
+      <c r="M26" s="39">
+        <f>Capex!M13</f>
+        <v/>
+      </c>
+      <c r="N26" s="39">
+        <f>Capex!N13</f>
+        <v/>
+      </c>
+      <c r="O26" s="39">
+        <f>Capex!O13</f>
+        <v/>
+      </c>
+      <c r="P26" s="39">
+        <f>Capex!P13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − Tax Depreciation  (Opening TAB ÷ 37yr blended ATO life)</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="G27" s="39">
+        <f>G25/37</f>
+        <v/>
+      </c>
+      <c r="H27" s="39">
+        <f>H25/37</f>
+        <v/>
+      </c>
+      <c r="I27" s="39">
+        <f>I25/37</f>
+        <v/>
+      </c>
+      <c r="J27" s="39">
+        <f>J25/37</f>
+        <v/>
+      </c>
+      <c r="K27" s="39">
+        <f>K25/37</f>
+        <v/>
+      </c>
+      <c r="L27" s="39">
+        <f>L25/37</f>
+        <v/>
+      </c>
+      <c r="M27" s="39">
+        <f>M25/37</f>
+        <v/>
+      </c>
+      <c r="N27" s="39">
+        <f>N25/37</f>
+        <v/>
+      </c>
+      <c r="O27" s="39">
+        <f>O25/37</f>
+        <v/>
+      </c>
+      <c r="P27" s="39">
+        <f>P25/37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = Closing TAB</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="n">
+        <v>3680.9</v>
+      </c>
+      <c r="C28" s="43" t="n">
+        <v>3881.9</v>
+      </c>
+      <c r="D28" s="43" t="n">
+        <v>4102.3</v>
+      </c>
+      <c r="E28" s="43" t="n">
+        <v>4341.8</v>
+      </c>
+      <c r="F28" s="43" t="n">
+        <v>4599.6</v>
+      </c>
+      <c r="G28" s="44">
+        <f>G25+G26-G27</f>
+        <v/>
+      </c>
+      <c r="H28" s="44">
+        <f>H25+H26-H27</f>
+        <v/>
+      </c>
+      <c r="I28" s="44">
+        <f>I25+I26-I27</f>
+        <v/>
+      </c>
+      <c r="J28" s="44">
+        <f>J25+J26-J27</f>
+        <v/>
+      </c>
+      <c r="K28" s="44">
+        <f>K25+K26-K27</f>
+        <v/>
+      </c>
+      <c r="L28" s="44">
+        <f>L25+L26-L27</f>
+        <v/>
+      </c>
+      <c r="M28" s="44">
+        <f>M25+M26-M27</f>
+        <v/>
+      </c>
+      <c r="N28" s="44">
+        <f>N25+N26-N27</f>
+        <v/>
+      </c>
+      <c r="O28" s="44">
+        <f>O25+O26-O27</f>
+        <v/>
+      </c>
+      <c r="P28" s="44">
+        <f>P25+P26-P27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>SECTION E — Accumulated Depreciation Comparison ($M)</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="16" t="n"/>
+      <c r="J30" s="16" t="n"/>
+      <c r="K30" s="16" t="n"/>
+      <c r="L30" s="16" t="n"/>
+      <c r="M30" s="16" t="n"/>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="16" t="n"/>
+      <c r="P30" s="16" t="n"/>
+      <c r="Q30" s="16" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accumulated Regulatory Dep. (closing)  ←  RAB Roll-Forward</t>
+        </is>
+      </c>
+      <c r="B31" s="26">
+        <f>'RAB Roll-Forward'!B51</f>
+        <v/>
+      </c>
+      <c r="C31" s="26">
+        <f>'RAB Roll-Forward'!C51</f>
+        <v/>
+      </c>
+      <c r="D31" s="26">
+        <f>'RAB Roll-Forward'!D51</f>
+        <v/>
+      </c>
+      <c r="E31" s="26">
+        <f>'RAB Roll-Forward'!E51</f>
+        <v/>
+      </c>
+      <c r="F31" s="26">
+        <f>'RAB Roll-Forward'!F51</f>
+        <v/>
+      </c>
+      <c r="G31" s="39">
+        <f>'RAB Roll-Forward'!G51</f>
+        <v/>
+      </c>
+      <c r="H31" s="39">
+        <f>'RAB Roll-Forward'!H51</f>
+        <v/>
+      </c>
+      <c r="I31" s="39">
+        <f>'RAB Roll-Forward'!I51</f>
+        <v/>
+      </c>
+      <c r="J31" s="39">
+        <f>'RAB Roll-Forward'!J51</f>
+        <v/>
+      </c>
+      <c r="K31" s="39">
+        <f>'RAB Roll-Forward'!K51</f>
+        <v/>
+      </c>
+      <c r="L31" s="39">
+        <f>'RAB Roll-Forward'!L51</f>
+        <v/>
+      </c>
+      <c r="M31" s="39">
+        <f>'RAB Roll-Forward'!M51</f>
+        <v/>
+      </c>
+      <c r="N31" s="39">
+        <f>'RAB Roll-Forward'!N51</f>
+        <v/>
+      </c>
+      <c r="O31" s="39">
+        <f>'RAB Roll-Forward'!O51</f>
+        <v/>
+      </c>
+      <c r="P31" s="39">
+        <f>'RAB Roll-Forward'!P51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accumulated Tax Dep. (opening)</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>4300</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>4399.1</v>
+      </c>
+      <c r="D32" s="26" t="n">
+        <v>4503.2</v>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>4612.8</v>
+      </c>
+      <c r="F32" s="26" t="n">
+        <v>4728.4</v>
+      </c>
+      <c r="G32" s="39">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="H32" s="39">
+        <f>G34</f>
+        <v/>
+      </c>
+      <c r="I32" s="39">
+        <f>H34</f>
+        <v/>
+      </c>
+      <c r="J32" s="39">
+        <f>I34</f>
+        <v/>
+      </c>
+      <c r="K32" s="39">
+        <f>J34</f>
+        <v/>
+      </c>
+      <c r="L32" s="39">
+        <f>K34</f>
+        <v/>
+      </c>
+      <c r="M32" s="39">
+        <f>L34</f>
+        <v/>
+      </c>
+      <c r="N32" s="39">
+        <f>M34</f>
+        <v/>
+      </c>
+      <c r="O32" s="39">
+        <f>N34</f>
+        <v/>
+      </c>
+      <c r="P32" s="39">
+        <f>O34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Current Year Tax Dep.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="E33" s="26" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="F33" s="26" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="G33" s="39">
+        <f>G27</f>
+        <v/>
+      </c>
+      <c r="H33" s="39">
+        <f>H27</f>
+        <v/>
+      </c>
+      <c r="I33" s="39">
+        <f>I27</f>
+        <v/>
+      </c>
+      <c r="J33" s="39">
+        <f>J27</f>
+        <v/>
+      </c>
+      <c r="K33" s="39">
+        <f>K27</f>
+        <v/>
+      </c>
+      <c r="L33" s="39">
+        <f>L27</f>
+        <v/>
+      </c>
+      <c r="M33" s="39">
+        <f>M27</f>
+        <v/>
+      </c>
+      <c r="N33" s="39">
+        <f>N27</f>
+        <v/>
+      </c>
+      <c r="O33" s="39">
+        <f>O27</f>
+        <v/>
+      </c>
+      <c r="P33" s="39">
+        <f>P27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = Accumulated Tax Dep. (closing)</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="n">
+        <v>4399.1</v>
+      </c>
+      <c r="C34" s="43" t="n">
+        <v>4503.2</v>
+      </c>
+      <c r="D34" s="43" t="n">
+        <v>4612.8</v>
+      </c>
+      <c r="E34" s="43" t="n">
+        <v>4728.4</v>
+      </c>
+      <c r="F34" s="43" t="n">
+        <v>4850.6</v>
+      </c>
+      <c r="G34" s="44">
+        <f>G32+G33</f>
+        <v/>
+      </c>
+      <c r="H34" s="44">
+        <f>H32+H33</f>
+        <v/>
+      </c>
+      <c r="I34" s="44">
+        <f>I32+I33</f>
+        <v/>
+      </c>
+      <c r="J34" s="44">
+        <f>J32+J33</f>
+        <v/>
+      </c>
+      <c r="K34" s="44">
+        <f>K32+K33</f>
+        <v/>
+      </c>
+      <c r="L34" s="44">
+        <f>L32+L33</f>
+        <v/>
+      </c>
+      <c r="M34" s="44">
+        <f>M32+M33</f>
+        <v/>
+      </c>
+      <c r="N34" s="44">
+        <f>N32+N33</f>
+        <v/>
+      </c>
+      <c r="O34" s="44">
+        <f>O32+O33</f>
+        <v/>
+      </c>
+      <c r="P34" s="44">
+        <f>P32+P33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total RAB − Total TAB  (AER vs ATO asset base gap)</t>
+        </is>
+      </c>
+      <c r="B35" s="46">
+        <f>'RAB Roll-Forward'!B44-B28</f>
+        <v/>
+      </c>
+      <c r="C35" s="46">
+        <f>'RAB Roll-Forward'!C44-C28</f>
+        <v/>
+      </c>
+      <c r="D35" s="46">
+        <f>'RAB Roll-Forward'!D44-D28</f>
+        <v/>
+      </c>
+      <c r="E35" s="46">
+        <f>'RAB Roll-Forward'!E44-E28</f>
+        <v/>
+      </c>
+      <c r="F35" s="46">
+        <f>'RAB Roll-Forward'!F44-F28</f>
+        <v/>
+      </c>
+      <c r="G35" s="46">
+        <f>'RAB Roll-Forward'!G44-G28</f>
+        <v/>
+      </c>
+      <c r="H35" s="46">
+        <f>'RAB Roll-Forward'!H44-H28</f>
+        <v/>
+      </c>
+      <c r="I35" s="46">
+        <f>'RAB Roll-Forward'!I44-I28</f>
+        <v/>
+      </c>
+      <c r="J35" s="46">
+        <f>'RAB Roll-Forward'!J44-J28</f>
+        <v/>
+      </c>
+      <c r="K35" s="46">
+        <f>'RAB Roll-Forward'!K44-K28</f>
+        <v/>
+      </c>
+      <c r="L35" s="46">
+        <f>'RAB Roll-Forward'!L44-L28</f>
+        <v/>
+      </c>
+      <c r="M35" s="46">
+        <f>'RAB Roll-Forward'!M44-M28</f>
+        <v/>
+      </c>
+      <c r="N35" s="46">
+        <f>'RAB Roll-Forward'!N44-N28</f>
+        <v/>
+      </c>
+      <c r="O35" s="46">
+        <f>'RAB Roll-Forward'!O44-O28</f>
+        <v/>
+      </c>
+      <c r="P35" s="46">
+        <f>'RAB Roll-Forward'!P44-P28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>SECTION F — Deferred Tax Liability (DTL) Roll-Forward ($M)  [AASB 112 | 30% corporate rate]</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="16" t="n"/>
+      <c r="H37" s="16" t="n"/>
+      <c r="I37" s="16" t="n"/>
+      <c r="J37" s="16" t="n"/>
+      <c r="K37" s="16" t="n"/>
+      <c r="L37" s="16" t="n"/>
+      <c r="M37" s="16" t="n"/>
+      <c r="N37" s="16" t="n"/>
+      <c r="O37" s="16" t="n"/>
+      <c r="P37" s="16" t="n"/>
+      <c r="Q37" s="16" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening DTL</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>510</v>
+      </c>
+      <c r="C38" s="26">
+        <f>B40</f>
+        <v/>
+      </c>
+      <c r="D38" s="26">
+        <f>C40</f>
+        <v/>
+      </c>
+      <c r="E38" s="26">
+        <f>D40</f>
+        <v/>
+      </c>
+      <c r="F38" s="26">
+        <f>E40</f>
+        <v/>
+      </c>
+      <c r="G38" s="39">
+        <f>F40</f>
+        <v/>
+      </c>
+      <c r="H38" s="39">
+        <f>G40</f>
+        <v/>
+      </c>
+      <c r="I38" s="39">
+        <f>H40</f>
+        <v/>
+      </c>
+      <c r="J38" s="39">
+        <f>I40</f>
+        <v/>
+      </c>
+      <c r="K38" s="39">
+        <f>J40</f>
+        <v/>
+      </c>
+      <c r="L38" s="39">
+        <f>K40</f>
+        <v/>
+      </c>
+      <c r="M38" s="39">
+        <f>L40</f>
+        <v/>
+      </c>
+      <c r="N38" s="39">
+        <f>M40</f>
+        <v/>
+      </c>
+      <c r="O38" s="39">
+        <f>N40</f>
+        <v/>
+      </c>
+      <c r="P38" s="39">
+        <f>O40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  + Movement: (Tax Dep − Acc Dep) × 30%  (positive = DTL grows as ATO deductions exceed accounting)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>-39.5</v>
+      </c>
+      <c r="C39" s="26" t="n">
+        <v>-40.6</v>
+      </c>
+      <c r="D39" s="26" t="n">
+        <v>-41.8</v>
+      </c>
+      <c r="E39" s="26" t="n">
+        <v>-43.1</v>
+      </c>
+      <c r="F39" s="26" t="n">
+        <v>-44.3</v>
+      </c>
+      <c r="G39" s="39">
+        <f>(G27-G18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="H39" s="39">
+        <f>(H27-H18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="I39" s="39">
+        <f>(I27-I18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="J39" s="39">
+        <f>(J27-J18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="K39" s="39">
+        <f>(K27-K18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="L39" s="39">
+        <f>(L27-L18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="M39" s="39">
+        <f>(M27-M18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="N39" s="39">
+        <f>(N27-N18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="O39" s="39">
+        <f>(O27-O18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="P39" s="39">
+        <f>(P27-P18)*Assumptions!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = Closing DTL  →  feeds Balance Sheet deferred tax</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="n">
+        <v>470.5</v>
+      </c>
+      <c r="C40" s="43" t="n">
+        <v>429.9</v>
+      </c>
+      <c r="D40" s="43" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="E40" s="43" t="n">
+        <v>345</v>
+      </c>
+      <c r="F40" s="43" t="n">
+        <v>300.7</v>
+      </c>
+      <c r="G40" s="44">
+        <f>G38+G39</f>
+        <v/>
+      </c>
+      <c r="H40" s="44">
+        <f>H38+H39</f>
+        <v/>
+      </c>
+      <c r="I40" s="44">
+        <f>I38+I39</f>
+        <v/>
+      </c>
+      <c r="J40" s="44">
+        <f>J38+J39</f>
+        <v/>
+      </c>
+      <c r="K40" s="44">
+        <f>K38+K39</f>
+        <v/>
+      </c>
+      <c r="L40" s="44">
+        <f>L38+L39</f>
+        <v/>
+      </c>
+      <c r="M40" s="44">
+        <f>M38+M39</f>
+        <v/>
+      </c>
+      <c r="N40" s="44">
+        <f>N38+N39</f>
+        <v/>
+      </c>
+      <c r="O40" s="44">
+        <f>O38+O39</f>
+        <v/>
+      </c>
+      <c r="P40" s="44">
+        <f>P38+P39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>SECTION G — PTRM Tax Allowance Reconciliation ($M)</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="16" t="n"/>
+      <c r="H42" s="16" t="n"/>
+      <c r="I42" s="16" t="n"/>
+      <c r="J42" s="16" t="n"/>
+      <c r="K42" s="16" t="n"/>
+      <c r="L42" s="16" t="n"/>
+      <c r="M42" s="16" t="n"/>
+      <c r="N42" s="16" t="n"/>
+      <c r="O42" s="16" t="n"/>
+      <c r="P42" s="16" t="n"/>
+      <c r="Q42" s="16" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Regulatory Taxable Income  (Return on RAB = Avg RAB × WACC)</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="C43" s="26" t="n">
+        <v>335.7</v>
+      </c>
+      <c r="D43" s="26" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="E43" s="26" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="F43" s="26" t="n">
+        <v>407.4</v>
+      </c>
+      <c r="G43" s="39">
+        <f>'RAB Roll-Forward'!G46</f>
+        <v/>
+      </c>
+      <c r="H43" s="39">
+        <f>'RAB Roll-Forward'!H46</f>
+        <v/>
+      </c>
+      <c r="I43" s="39">
+        <f>'RAB Roll-Forward'!I46</f>
+        <v/>
+      </c>
+      <c r="J43" s="39">
+        <f>'RAB Roll-Forward'!J46</f>
+        <v/>
+      </c>
+      <c r="K43" s="39">
+        <f>'RAB Roll-Forward'!K46</f>
+        <v/>
+      </c>
+      <c r="L43" s="39">
+        <f>'RAB Roll-Forward'!L46</f>
+        <v/>
+      </c>
+      <c r="M43" s="39">
+        <f>'RAB Roll-Forward'!M46</f>
+        <v/>
+      </c>
+      <c r="N43" s="39">
+        <f>'RAB Roll-Forward'!N46</f>
+        <v/>
+      </c>
+      <c r="O43" s="39">
+        <f>'RAB Roll-Forward'!O46</f>
+        <v/>
+      </c>
+      <c r="P43" s="39">
+        <f>'RAB Roll-Forward'!P46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross Tax  (× 30% corporate rate)</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="C44" s="26" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="D44" s="26" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="E44" s="26" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="F44" s="26" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="G44" s="39">
+        <f>G43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="H44" s="39">
+        <f>H43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="I44" s="39">
+        <f>I43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="J44" s="39">
+        <f>J43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="K44" s="39">
+        <f>K43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="L44" s="39">
+        <f>L43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="M44" s="39">
+        <f>M43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="N44" s="39">
+        <f>N43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="O44" s="39">
+        <f>O43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="P44" s="39">
+        <f>P43*Assumptions!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: Gamma Benefit  (× gamma × 30%)  AER imputation credit offset</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="C45" s="26" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="E45" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="F45" s="26" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G45" s="39">
+        <f>G43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="H45" s="39">
+        <f>H43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="I45" s="39">
+        <f>I43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="J45" s="39">
+        <f>J43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="K45" s="39">
+        <f>K43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="L45" s="39">
+        <f>L43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="M45" s="39">
+        <f>M43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="N45" s="39">
+        <f>N43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="O45" s="39">
+        <f>O43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+      <c r="P45" s="39">
+        <f>P43*Assumptions!$B$11*Assumptions!$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net PTRM Tax Allowance  (Gross − Gamma)</t>
+        </is>
+      </c>
+      <c r="B46" s="43" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="C46" s="43" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="D46" s="43" t="n">
+        <v>44</v>
+      </c>
+      <c r="E46" s="43" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F46" s="43" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G46" s="44">
+        <f>G44-G45</f>
+        <v/>
+      </c>
+      <c r="H46" s="44">
+        <f>H44-H45</f>
+        <v/>
+      </c>
+      <c r="I46" s="44">
+        <f>I44-I45</f>
+        <v/>
+      </c>
+      <c r="J46" s="44">
+        <f>J44-J45</f>
+        <v/>
+      </c>
+      <c r="K46" s="44">
+        <f>K44-K45</f>
+        <v/>
+      </c>
+      <c r="L46" s="44">
+        <f>L44-L45</f>
+        <v/>
+      </c>
+      <c r="M46" s="44">
+        <f>M44-M45</f>
+        <v/>
+      </c>
+      <c r="N46" s="44">
+        <f>N44-N45</f>
+        <v/>
+      </c>
+      <c r="O46" s="44">
+        <f>O44-O45</f>
+        <v/>
+      </c>
+      <c r="P46" s="44">
+        <f>P44-P45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cross-Check vs PTRM tab  (= 0 if matched)</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="58">
+        <f>G46-PTRM!G8</f>
+        <v/>
+      </c>
+      <c r="H47" s="58">
+        <f>H46-PTRM!H8</f>
+        <v/>
+      </c>
+      <c r="I47" s="58">
+        <f>I46-PTRM!I8</f>
+        <v/>
+      </c>
+      <c r="J47" s="58">
+        <f>J46-PTRM!J8</f>
+        <v/>
+      </c>
+      <c r="K47" s="58">
+        <f>K46-PTRM!K8</f>
+        <v/>
+      </c>
+      <c r="L47" s="58">
+        <f>L46-PTRM!L8</f>
+        <v/>
+      </c>
+      <c r="M47" s="58">
+        <f>M46-PTRM!M8</f>
+        <v/>
+      </c>
+      <c r="N47" s="58">
+        <f>N46-PTRM!N8</f>
+        <v/>
+      </c>
+      <c r="O47" s="58">
+        <f>O46-PTRM!O8</f>
+        <v/>
+      </c>
+      <c r="P47" s="58">
+        <f>P46-PTRM!P8</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3900,7 +8735,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="57" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>STRATEGIC INITIATIVES — Revenue Growth &amp; Cost Reduction Pipeline</t>
         </is>
@@ -3990,26 +8825,26 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>REVENUE ENHANCEMENT ($M — annual benefit)</t>
         </is>
       </c>
-      <c r="B4" s="59" t="n"/>
-      <c r="C4" s="59" t="n"/>
-      <c r="D4" s="59" t="n"/>
-      <c r="E4" s="59" t="n"/>
-      <c r="F4" s="59" t="n"/>
-      <c r="G4" s="59" t="n"/>
-      <c r="H4" s="59" t="n"/>
-      <c r="I4" s="59" t="n"/>
-      <c r="J4" s="59" t="n"/>
-      <c r="K4" s="59" t="n"/>
-      <c r="L4" s="59" t="n"/>
-      <c r="M4" s="59" t="n"/>
-      <c r="N4" s="59" t="n"/>
-      <c r="O4" s="59" t="n"/>
-      <c r="P4" s="59" t="n"/>
+      <c r="B4" s="61" t="n"/>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="61" t="n"/>
+      <c r="F4" s="61" t="n"/>
+      <c r="G4" s="61" t="n"/>
+      <c r="H4" s="61" t="n"/>
+      <c r="I4" s="61" t="n"/>
+      <c r="J4" s="61" t="n"/>
+      <c r="K4" s="61" t="n"/>
+      <c r="L4" s="61" t="n"/>
+      <c r="M4" s="61" t="n"/>
+      <c r="N4" s="61" t="n"/>
+      <c r="O4" s="61" t="n"/>
+      <c r="P4" s="61" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
@@ -4242,26 +9077,26 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>OPEX REDUCTION INITIATIVES ($M — annual saving)</t>
         </is>
       </c>
-      <c r="B10" s="59" t="n"/>
-      <c r="C10" s="59" t="n"/>
-      <c r="D10" s="59" t="n"/>
-      <c r="E10" s="59" t="n"/>
-      <c r="F10" s="59" t="n"/>
-      <c r="G10" s="59" t="n"/>
-      <c r="H10" s="59" t="n"/>
-      <c r="I10" s="59" t="n"/>
-      <c r="J10" s="59" t="n"/>
-      <c r="K10" s="59" t="n"/>
-      <c r="L10" s="59" t="n"/>
-      <c r="M10" s="59" t="n"/>
-      <c r="N10" s="59" t="n"/>
-      <c r="O10" s="59" t="n"/>
-      <c r="P10" s="59" t="n"/>
+      <c r="B10" s="61" t="n"/>
+      <c r="C10" s="61" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="61" t="n"/>
+      <c r="F10" s="61" t="n"/>
+      <c r="G10" s="61" t="n"/>
+      <c r="H10" s="61" t="n"/>
+      <c r="I10" s="61" t="n"/>
+      <c r="J10" s="61" t="n"/>
+      <c r="K10" s="61" t="n"/>
+      <c r="L10" s="61" t="n"/>
+      <c r="M10" s="61" t="n"/>
+      <c r="N10" s="61" t="n"/>
+      <c r="O10" s="61" t="n"/>
+      <c r="P10" s="61" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -4494,26 +9329,26 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>FINANCE COST REDUCTION ($M — annual saving)</t>
         </is>
       </c>
-      <c r="B16" s="59" t="n"/>
-      <c r="C16" s="59" t="n"/>
-      <c r="D16" s="59" t="n"/>
-      <c r="E16" s="59" t="n"/>
-      <c r="F16" s="59" t="n"/>
-      <c r="G16" s="59" t="n"/>
-      <c r="H16" s="59" t="n"/>
-      <c r="I16" s="59" t="n"/>
-      <c r="J16" s="59" t="n"/>
-      <c r="K16" s="59" t="n"/>
-      <c r="L16" s="59" t="n"/>
-      <c r="M16" s="59" t="n"/>
-      <c r="N16" s="59" t="n"/>
-      <c r="O16" s="59" t="n"/>
-      <c r="P16" s="59" t="n"/>
+      <c r="B16" s="61" t="n"/>
+      <c r="C16" s="61" t="n"/>
+      <c r="D16" s="61" t="n"/>
+      <c r="E16" s="61" t="n"/>
+      <c r="F16" s="61" t="n"/>
+      <c r="G16" s="61" t="n"/>
+      <c r="H16" s="61" t="n"/>
+      <c r="I16" s="61" t="n"/>
+      <c r="J16" s="61" t="n"/>
+      <c r="K16" s="61" t="n"/>
+      <c r="L16" s="61" t="n"/>
+      <c r="M16" s="61" t="n"/>
+      <c r="N16" s="61" t="n"/>
+      <c r="O16" s="61" t="n"/>
+      <c r="P16" s="61" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="inlineStr">
@@ -4694,26 +9529,26 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>DEPRECIATION REDUCTION ($M — annual saving)</t>
         </is>
       </c>
-      <c r="B21" s="59" t="n"/>
-      <c r="C21" s="59" t="n"/>
-      <c r="D21" s="59" t="n"/>
-      <c r="E21" s="59" t="n"/>
-      <c r="F21" s="59" t="n"/>
-      <c r="G21" s="59" t="n"/>
-      <c r="H21" s="59" t="n"/>
-      <c r="I21" s="59" t="n"/>
-      <c r="J21" s="59" t="n"/>
-      <c r="K21" s="59" t="n"/>
-      <c r="L21" s="59" t="n"/>
-      <c r="M21" s="59" t="n"/>
-      <c r="N21" s="59" t="n"/>
-      <c r="O21" s="59" t="n"/>
-      <c r="P21" s="59" t="n"/>
+      <c r="B21" s="61" t="n"/>
+      <c r="C21" s="61" t="n"/>
+      <c r="D21" s="61" t="n"/>
+      <c r="E21" s="61" t="n"/>
+      <c r="F21" s="61" t="n"/>
+      <c r="G21" s="61" t="n"/>
+      <c r="H21" s="61" t="n"/>
+      <c r="I21" s="61" t="n"/>
+      <c r="J21" s="61" t="n"/>
+      <c r="K21" s="61" t="n"/>
+      <c r="L21" s="61" t="n"/>
+      <c r="M21" s="61" t="n"/>
+      <c r="N21" s="61" t="n"/>
+      <c r="O21" s="61" t="n"/>
+      <c r="P21" s="61" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
@@ -4991,7 +9826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -6217,7 +11052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -7590,7 +12425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -8715,7 +13550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -8744,7 +13579,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>MODEL CHECKS — Balance Sheet | CFS Roll-Forward | RAB Integrity</t>
         </is>
@@ -8996,63 +13831,63 @@
           <t xml:space="preserve">  Discrepancy (target = 0)</t>
         </is>
       </c>
-      <c r="B7" s="61">
+      <c r="B7" s="63">
         <f>B5-B6</f>
         <v/>
       </c>
-      <c r="C7" s="61">
+      <c r="C7" s="63">
         <f>C5-C6</f>
         <v/>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="63">
         <f>D5-D6</f>
         <v/>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="63">
         <f>E5-E6</f>
         <v/>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="63">
         <f>F5-F6</f>
         <v/>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="64">
         <f>G5-G6</f>
         <v/>
       </c>
-      <c r="H7" s="62">
+      <c r="H7" s="64">
         <f>H5-H6</f>
         <v/>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="64">
         <f>I5-I6</f>
         <v/>
       </c>
-      <c r="J7" s="62">
+      <c r="J7" s="64">
         <f>J5-J6</f>
         <v/>
       </c>
-      <c r="K7" s="62">
+      <c r="K7" s="64">
         <f>K5-K6</f>
         <v/>
       </c>
-      <c r="L7" s="62">
+      <c r="L7" s="64">
         <f>L5-L6</f>
         <v/>
       </c>
-      <c r="M7" s="62">
+      <c r="M7" s="64">
         <f>M5-M6</f>
         <v/>
       </c>
-      <c r="N7" s="62">
+      <c r="N7" s="64">
         <f>N5-N6</f>
         <v/>
       </c>
-      <c r="O7" s="62">
+      <c r="O7" s="64">
         <f>O5-O6</f>
         <v/>
       </c>
-      <c r="P7" s="62">
+      <c r="P7" s="64">
         <f>P5-P6</f>
         <v/>
       </c>
@@ -9220,63 +14055,63 @@
           <t xml:space="preserve">  Discrepancy (target = 0)</t>
         </is>
       </c>
-      <c r="B12" s="61">
+      <c r="B12" s="63">
         <f>B10-B11</f>
         <v/>
       </c>
-      <c r="C12" s="61">
+      <c r="C12" s="63">
         <f>C10-C11</f>
         <v/>
       </c>
-      <c r="D12" s="61">
+      <c r="D12" s="63">
         <f>D10-D11</f>
         <v/>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="63">
         <f>E10-E11</f>
         <v/>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="63">
         <f>F10-F11</f>
         <v/>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="64">
         <f>G10-G11</f>
         <v/>
       </c>
-      <c r="H12" s="62">
+      <c r="H12" s="64">
         <f>H10-H11</f>
         <v/>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="64">
         <f>I10-I11</f>
         <v/>
       </c>
-      <c r="J12" s="62">
+      <c r="J12" s="64">
         <f>J10-J11</f>
         <v/>
       </c>
-      <c r="K12" s="62">
+      <c r="K12" s="64">
         <f>K10-K11</f>
         <v/>
       </c>
-      <c r="L12" s="62">
+      <c r="L12" s="64">
         <f>L10-L11</f>
         <v/>
       </c>
-      <c r="M12" s="62">
+      <c r="M12" s="64">
         <f>M10-M11</f>
         <v/>
       </c>
-      <c r="N12" s="62">
+      <c r="N12" s="64">
         <f>N10-N11</f>
         <v/>
       </c>
-      <c r="O12" s="62">
+      <c r="O12" s="64">
         <f>O10-O11</f>
         <v/>
       </c>
-      <c r="P12" s="62">
+      <c r="P12" s="64">
         <f>P10-P11</f>
         <v/>
       </c>
@@ -9377,63 +14212,63 @@
           <t xml:space="preserve">  Discrepancy (target = 0)</t>
         </is>
       </c>
-      <c r="B16" s="61">
+      <c r="B16" s="63">
         <f>B15-B15</f>
         <v/>
       </c>
-      <c r="C16" s="61">
+      <c r="C16" s="63">
         <f>C15-C15</f>
         <v/>
       </c>
-      <c r="D16" s="61">
+      <c r="D16" s="63">
         <f>D15-D15</f>
         <v/>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="63">
         <f>E15-E15</f>
         <v/>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="63">
         <f>F15-F15</f>
         <v/>
       </c>
-      <c r="G16" s="62">
+      <c r="G16" s="64">
         <f>G15-G15</f>
         <v/>
       </c>
-      <c r="H16" s="62">
+      <c r="H16" s="64">
         <f>H15-H15</f>
         <v/>
       </c>
-      <c r="I16" s="62">
+      <c r="I16" s="64">
         <f>I15-I15</f>
         <v/>
       </c>
-      <c r="J16" s="62">
+      <c r="J16" s="64">
         <f>J15-J15</f>
         <v/>
       </c>
-      <c r="K16" s="62">
+      <c r="K16" s="64">
         <f>K15-K15</f>
         <v/>
       </c>
-      <c r="L16" s="62">
+      <c r="L16" s="64">
         <f>L15-L15</f>
         <v/>
       </c>
-      <c r="M16" s="62">
+      <c r="M16" s="64">
         <f>M15-M15</f>
         <v/>
       </c>
-      <c r="N16" s="62">
+      <c r="N16" s="64">
         <f>N15-N15</f>
         <v/>
       </c>
-      <c r="O16" s="62">
+      <c r="O16" s="64">
         <f>O15-O15</f>
         <v/>
       </c>
-      <c r="P16" s="62">
+      <c r="P16" s="64">
         <f>P15-P15</f>
         <v/>
       </c>

--- a/three_way_finance_model.xlsx
+++ b/three_way_finance_model.xlsx
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="D18" s="1" t="n"/>
